--- a/VT_REG1_TRA_V12.xlsx
+++ b/VT_REG1_TRA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BA8ACF-761F-4F59-8A9B-B9B8F0339AD4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CD18D5-2F23-4F57-878A-FB6AA4430DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" tabRatio="901" activeTab="4"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -27,12 +27,17 @@
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,12 +45,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,14 +68,14 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -184,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -210,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0">
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -283,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -369,7 +374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P13" authorId="2" shapeId="0">
+    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -462,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="1" shapeId="0">
+    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -487,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R13" authorId="2" shapeId="0">
+    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -550,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="2" shapeId="0">
+    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -798,14 +803,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -919,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="1" shapeId="0">
+    <comment ref="T3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -945,7 +950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="2" shapeId="0">
+    <comment ref="U3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1018,7 +1023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="2" shapeId="0">
+    <comment ref="V3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1071,7 +1076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="2" shapeId="0">
+    <comment ref="W3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1104,7 +1109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U10" authorId="2" shapeId="0">
+    <comment ref="U10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1197,7 +1202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="1" shapeId="0">
+    <comment ref="V10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1222,7 +1227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="2" shapeId="0">
+    <comment ref="W10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O11" authorId="2" shapeId="0">
+    <comment ref="O11" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1533,7 +1538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="192">
   <si>
     <t>CommName</t>
   </si>
@@ -2088,19 +2093,40 @@
   </si>
   <si>
     <t>Bpass*km</t>
+  </si>
+  <si>
+    <t>jklh</t>
+  </si>
+  <si>
+    <t>VBNC</t>
+  </si>
+  <si>
+    <t>NBNBVCN</t>
+  </si>
+  <si>
+    <t>VBN</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>HGJG</t>
+  </si>
+  <si>
+    <t>CVBNC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="186" formatCode="0.000"/>
-    <numFmt numFmtId="187" formatCode="General_)"/>
-    <numFmt numFmtId="195" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="General_)"/>
+    <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2130,32 +2156,6 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -2622,171 +2622,158 @@
   </borders>
   <cellStyleXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="28" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="10" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="22" fillId="10" borderId="0" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="20" fillId="8" borderId="4" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="18" fillId="10" borderId="0" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="4" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="8" borderId="5" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="5" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="20" fillId="8" borderId="6" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="6" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2795,42 +2782,40 @@
     <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="187" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="3"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2839,40 +2824,36 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="15" borderId="10" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="15" borderId="10" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="15" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="15" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="15" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="15" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="15" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="15" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="10" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="22" fillId="10" borderId="16" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="22" fillId="10" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="22" fillId="10" borderId="14" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="10" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="10" borderId="16" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="10" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="10" borderId="14" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="28" fillId="13" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="13" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2882,47 +2863,45 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="13" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="13" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="13" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="13" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -2930,24 +2909,24 @@
     <cellStyle name="60% - Accent2" xfId="3" builtinId="36"/>
     <cellStyle name="Accent2" xfId="4" builtinId="33"/>
     <cellStyle name="Calculation" xfId="5" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="6"/>
+    <cellStyle name="Comma 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Good" xfId="7" builtinId="26"/>
     <cellStyle name="Input" xfId="8" builtinId="20"/>
     <cellStyle name="Neutral" xfId="9" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="10"/>
-    <cellStyle name="Normal 2" xfId="11"/>
-    <cellStyle name="Normal 4" xfId="12"/>
-    <cellStyle name="Normal 4 2" xfId="13"/>
-    <cellStyle name="Normal 8" xfId="14"/>
-    <cellStyle name="Normal 9 2" xfId="15"/>
-    <cellStyle name="Normale_B2020" xfId="16"/>
+    <cellStyle name="Normal 10" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 4" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 8" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 9 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normale_B2020" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="Percent" xfId="17" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="18"/>
-    <cellStyle name="Percent 3" xfId="19"/>
-    <cellStyle name="Percent 4" xfId="20"/>
-    <cellStyle name="Percent 5" xfId="21"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="22"/>
+    <cellStyle name="Percent 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Percent 3" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Percent 4" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Percent 5" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3942,7 +3921,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -4077,7 +4056,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -4867,8 +4846,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:AA31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -4883,8 +4862,8 @@
     <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="X1" s="24" t="s">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="X1" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Y1" s="1" t="s">
@@ -4897,1243 +4876,1204 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="7"/>
-      <c r="D2" s="54" t="s">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="M2" s="54" t="s">
+      <c r="M2" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="O2" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="Q2" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="R2" s="54" t="s">
+      <c r="R2" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="S2" s="54" t="s">
+      <c r="S2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="54" t="s">
+      <c r="T2" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="54" t="s">
+      <c r="U2" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="54" t="s">
+      <c r="V2" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="53" t="s">
+      <c r="Y2" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AA2" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C3" s="74" t="s">
+    <row r="3" spans="2:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C3" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="55" t="s">
+      <c r="O3" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="Q3" s="55" t="s">
+      <c r="Q3" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="S3" s="55" t="s">
+      <c r="S3" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="55" t="s">
+      <c r="T3" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="V3" s="55" t="s">
+      <c r="V3" s="42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B4" s="52"/>
-      <c r="C4" s="96" t="s">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B4" s="39"/>
+      <c r="C4" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="97"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="56" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="82"/>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B5" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="98">
+      <c r="D5" s="83">
         <f>[2]EB1!D16</f>
         <v>231.76075</v>
       </c>
-      <c r="E5" s="98">
+      <c r="E5" s="83">
         <f>[2]EB1!E16</f>
         <v>2063.9171999999999</v>
       </c>
-      <c r="F5" s="98">
+      <c r="F5" s="83">
         <f>[2]EB1!F16</f>
         <v>0</v>
       </c>
-      <c r="G5" s="98">
+      <c r="G5" s="83">
         <f>[2]EB1!G16</f>
         <v>862.053</v>
       </c>
-      <c r="H5" s="98">
+      <c r="H5" s="83">
         <f>[2]EB1!H16</f>
         <v>72.9495</v>
       </c>
-      <c r="I5" s="98">
+      <c r="I5" s="83">
         <f>[2]EB1!I16</f>
         <v>190.17599999999999</v>
       </c>
-      <c r="J5" s="98">
+      <c r="J5" s="83">
         <f>[2]EB1!J16</f>
         <v>3.1680000000000001</v>
       </c>
-      <c r="K5" s="98">
+      <c r="K5" s="83">
         <f>[2]EB1!K16</f>
         <v>0</v>
       </c>
-      <c r="L5" s="98">
+      <c r="L5" s="83">
         <f>[2]EB1!L16</f>
         <v>15.38</v>
       </c>
-      <c r="M5" s="98">
+      <c r="M5" s="83">
         <f>[2]EB1!M16</f>
         <v>0.92</v>
       </c>
-      <c r="N5" s="99">
+      <c r="N5" s="84">
         <f>[2]EB1!N16</f>
         <v>0</v>
       </c>
-      <c r="O5" s="98">
+      <c r="O5" s="83">
         <f>[2]EB1!O16</f>
         <v>895.44524999999999</v>
       </c>
-      <c r="P5" s="98">
+      <c r="P5" s="83">
         <f>[2]EB1!P16</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="98">
+      <c r="Q5" s="83">
         <f>[2]EB1!Q16</f>
         <v>0</v>
       </c>
-      <c r="R5" s="98">
+      <c r="R5" s="83">
         <f>[2]EB1!R16</f>
         <v>50</v>
       </c>
-      <c r="S5" s="98">
+      <c r="S5" s="83">
         <f>[2]EB1!S16</f>
         <v>0</v>
       </c>
-      <c r="T5" s="98">
+      <c r="T5" s="83">
         <f>[2]EB1!T16</f>
         <v>432.74250000000001</v>
       </c>
-      <c r="U5" s="98">
+      <c r="U5" s="83">
         <f>[2]EB1!U16</f>
         <v>1435.8710000000001</v>
       </c>
-      <c r="V5" s="100">
+      <c r="V5" s="85">
         <f>SUM(D5:U5)</f>
         <v>6254.3832000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="56" t="s">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B6" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="98">
+      <c r="D6" s="83">
         <f>[2]EB1!D17</f>
         <v>37.001249999999999</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="83">
         <f>[2]EB1!E17</f>
         <v>700.69200000000001</v>
       </c>
-      <c r="F6" s="98">
+      <c r="F6" s="83">
         <f>[2]EB1!F17</f>
         <v>0</v>
       </c>
-      <c r="G6" s="98">
+      <c r="G6" s="83">
         <f>[2]EB1!G17</f>
         <v>368.84399999999999</v>
       </c>
-      <c r="H6" s="98">
+      <c r="H6" s="83">
         <f>[2]EB1!H17</f>
         <v>1.677</v>
       </c>
-      <c r="I6" s="98">
+      <c r="I6" s="83">
         <f>[2]EB1!I17</f>
         <v>31.602</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="83">
         <f>[2]EB1!J17</f>
         <v>5.72</v>
       </c>
-      <c r="K6" s="98">
+      <c r="K6" s="83">
         <f>[2]EB1!K17</f>
         <v>0</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="83">
         <f>[2]EB1!L17</f>
         <v>19.32</v>
       </c>
-      <c r="M6" s="98">
+      <c r="M6" s="83">
         <f>[2]EB1!M17</f>
         <v>0.24199999999999999</v>
       </c>
-      <c r="N6" s="99">
+      <c r="N6" s="84">
         <f>[2]EB1!N17</f>
         <v>0</v>
       </c>
-      <c r="O6" s="98">
+      <c r="O6" s="83">
         <f>[2]EB1!O17</f>
         <v>39</v>
       </c>
-      <c r="P6" s="98">
+      <c r="P6" s="83">
         <f>[2]EB1!P17</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="98">
+      <c r="Q6" s="83">
         <f>[2]EB1!Q17</f>
         <v>0</v>
       </c>
-      <c r="R6" s="98">
+      <c r="R6" s="83">
         <f>[2]EB1!R17</f>
         <v>7.5</v>
       </c>
-      <c r="S6" s="98">
+      <c r="S6" s="83">
         <f>[2]EB1!S17</f>
         <v>0.60850000000000004</v>
       </c>
-      <c r="T6" s="98">
+      <c r="T6" s="83">
         <f>[2]EB1!T17</f>
         <v>127.32299999999999</v>
       </c>
-      <c r="U6" s="98">
+      <c r="U6" s="83">
         <f>[2]EB1!U17</f>
         <v>1263.6955</v>
       </c>
-      <c r="V6" s="100">
+      <c r="V6" s="85">
         <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
         <v>2603.2252500000004</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="56" t="s">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B7" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="98">
+      <c r="D7" s="83">
         <f>[2]EB1!D18</f>
         <v>1233.0409000000002</v>
       </c>
-      <c r="E7" s="98">
+      <c r="E7" s="83">
         <f>[2]EB1!E18</f>
         <v>1774.8644000000002</v>
       </c>
-      <c r="F7" s="98">
+      <c r="F7" s="83">
         <f>[2]EB1!F18</f>
         <v>0</v>
       </c>
-      <c r="G7" s="98">
+      <c r="G7" s="83">
         <f>[2]EB1!G18</f>
         <v>298.68</v>
       </c>
-      <c r="H7" s="98">
+      <c r="H7" s="83">
         <f>[2]EB1!H18</f>
         <v>36.356499999999997</v>
       </c>
-      <c r="I7" s="98">
+      <c r="I7" s="83">
         <f>[2]EB1!I18</f>
         <v>142.97149999999999</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="83">
         <f>[2]EB1!J18</f>
         <v>7.766</v>
       </c>
-      <c r="K7" s="98">
+      <c r="K7" s="83">
         <f>[2]EB1!K18</f>
         <v>44.066000000000003</v>
       </c>
-      <c r="L7" s="98">
+      <c r="L7" s="83">
         <f>[2]EB1!L18</f>
         <v>286.0505</v>
       </c>
-      <c r="M7" s="98">
+      <c r="M7" s="83">
         <f>[2]EB1!M18</f>
         <v>191.57300000000001</v>
       </c>
-      <c r="N7" s="99">
+      <c r="N7" s="84">
         <f>[2]EB1!N18</f>
         <v>0</v>
       </c>
-      <c r="O7" s="98">
+      <c r="O7" s="83">
         <f>[2]EB1!O18</f>
         <v>541.25324999999998</v>
       </c>
-      <c r="P7" s="98">
+      <c r="P7" s="83">
         <f>[2]EB1!P18</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="98">
+      <c r="Q7" s="83">
         <f>[2]EB1!Q18</f>
         <v>0</v>
       </c>
-      <c r="R7" s="98">
+      <c r="R7" s="83">
         <f>[2]EB1!R18</f>
         <v>0</v>
       </c>
-      <c r="S7" s="98">
+      <c r="S7" s="83">
         <f>[2]EB1!S18</f>
         <v>58.595999999999997</v>
       </c>
-      <c r="T7" s="98">
+      <c r="T7" s="83">
         <f>[2]EB1!T18</f>
         <v>316.79149999999998</v>
       </c>
-      <c r="U7" s="98">
+      <c r="U7" s="83">
         <f>[2]EB1!U18</f>
         <v>2044.222</v>
       </c>
-      <c r="V7" s="100">
+      <c r="V7" s="85">
         <f t="shared" si="0"/>
         <v>6976.2315499999995</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="56" t="s">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B8" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="98">
+      <c r="D8" s="83">
         <f>[2]EB1!D19</f>
         <v>28.665000000000003</v>
       </c>
-      <c r="E8" s="98">
+      <c r="E8" s="83">
         <f>[2]EB1!E19</f>
         <v>80.482399999999998</v>
       </c>
-      <c r="F8" s="98">
+      <c r="F8" s="83">
         <f>[2]EB1!F19</f>
         <v>0</v>
       </c>
-      <c r="G8" s="98">
+      <c r="G8" s="83">
         <f>[2]EB1!G19</f>
         <v>366.58800000000002</v>
       </c>
-      <c r="H8" s="98">
+      <c r="H8" s="83">
         <f>[2]EB1!H19</f>
         <v>0.47299999999999998</v>
       </c>
-      <c r="I8" s="98">
+      <c r="I8" s="83">
         <f>[2]EB1!I19</f>
         <v>16.169</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="83">
         <f>[2]EB1!J19</f>
         <v>1.716</v>
       </c>
-      <c r="K8" s="98">
+      <c r="K8" s="83">
         <f>[2]EB1!K19</f>
         <v>0</v>
       </c>
-      <c r="L8" s="98">
+      <c r="L8" s="83">
         <f>[2]EB1!L19</f>
         <v>13.74</v>
       </c>
-      <c r="M8" s="98">
+      <c r="M8" s="83">
         <f>[2]EB1!M19</f>
         <v>0</v>
       </c>
-      <c r="N8" s="99">
+      <c r="N8" s="84">
         <f>[2]EB1!N19</f>
         <v>0</v>
       </c>
-      <c r="O8" s="98">
+      <c r="O8" s="83">
         <f>[2]EB1!O19</f>
         <v>47.314499999999995</v>
       </c>
-      <c r="P8" s="98">
+      <c r="P8" s="83">
         <f>[2]EB1!P19</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="98">
+      <c r="Q8" s="83">
         <f>[2]EB1!Q19</f>
         <v>0</v>
       </c>
-      <c r="R8" s="98">
+      <c r="R8" s="83">
         <f>[2]EB1!R19</f>
         <v>0</v>
       </c>
-      <c r="S8" s="98">
+      <c r="S8" s="83">
         <f>[2]EB1!S19</f>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="T8" s="98">
+      <c r="T8" s="83">
         <f>[2]EB1!T19</f>
         <v>7.7869999999999999</v>
       </c>
-      <c r="U8" s="98">
+      <c r="U8" s="83">
         <f>[2]EB1!U19</f>
         <v>9.6930000000000014</v>
       </c>
-      <c r="V8" s="100">
+      <c r="V8" s="85">
         <f t="shared" si="0"/>
         <v>572.62840000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="56" t="s">
+    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="98">
+      <c r="D9" s="83">
         <f>[2]EB1!D20</f>
         <v>0.36140000000000005</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="47">
         <f>[2]EB1!E20</f>
         <v>8.4995999999999992</v>
       </c>
-      <c r="F9" s="98">
+      <c r="F9" s="83">
         <f>[2]EB1!F20</f>
         <v>0</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="47">
         <f>[2]EB1!G20</f>
         <v>3856.2855</v>
       </c>
-      <c r="H9" s="98">
+      <c r="H9" s="83">
         <f>[2]EB1!H20</f>
         <v>1047.652</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="47">
         <f>[2]EB1!I20</f>
         <v>94.230999999999995</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="47">
         <f>[2]EB1!J20</f>
         <v>2394.2159999999999</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="83">
         <f>[2]EB1!K20</f>
         <v>0</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="83">
         <f>[2]EB1!L20</f>
         <v>33.24</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="83">
         <f>[2]EB1!M20</f>
         <v>0</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="83">
         <f>[2]EB1!N20</f>
         <v>0</v>
       </c>
-      <c r="O9" s="60">
+      <c r="O9" s="47">
         <f>[2]EB1!O20</f>
         <v>120.75</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="83">
         <f>[2]EB1!P20</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="83">
         <f>[2]EB1!Q20</f>
         <v>0</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="83">
         <f>[2]EB1!R20</f>
         <v>0</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="83">
         <f>[2]EB1!S20</f>
         <v>0</v>
       </c>
-      <c r="T9" s="98">
+      <c r="T9" s="83">
         <f>[2]EB1!T20</f>
         <v>0</v>
       </c>
-      <c r="U9" s="60">
+      <c r="U9" s="47">
         <f>[2]EB1!U20</f>
         <v>132.98599999999999</v>
       </c>
-      <c r="V9" s="100">
+      <c r="V9" s="85">
         <f t="shared" si="0"/>
         <v>7688.2214999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="56" t="s">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B10" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="46">
         <f>[2]EB1!D21</f>
         <v>773.00014999999871</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="46">
         <f>[2]EB1!E21</f>
         <v>0</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="46">
         <f>[2]EB1!F21</f>
         <v>0</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="46">
         <f>[2]EB1!G21</f>
         <v>0</v>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="46">
         <f>[2]EB1!H21</f>
         <v>0</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="46">
         <f>[2]EB1!I21</f>
         <v>0</v>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="46">
         <f>[2]EB1!J21</f>
         <v>0</v>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="46">
         <f>[2]EB1!K21</f>
         <v>0</v>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="46">
         <f>[2]EB1!L21</f>
         <v>0</v>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="46">
         <f>[2]EB1!M21</f>
         <v>0</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="46">
         <f>[2]EB1!N21</f>
         <v>0</v>
       </c>
-      <c r="O10" s="59">
+      <c r="O10" s="46">
         <f>[2]EB1!O21</f>
         <v>0</v>
       </c>
-      <c r="P10" s="59">
+      <c r="P10" s="46">
         <f>[2]EB1!P21</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="59">
+      <c r="Q10" s="46">
         <f>[2]EB1!Q21</f>
         <v>0</v>
       </c>
-      <c r="R10" s="59">
+      <c r="R10" s="46">
         <f>[2]EB1!R21</f>
         <v>0</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="46">
         <f>[2]EB1!S21</f>
         <v>0</v>
       </c>
-      <c r="T10" s="59">
+      <c r="T10" s="46">
         <f>[2]EB1!T21</f>
         <v>313.51900000000001</v>
       </c>
-      <c r="U10" s="59">
+      <c r="U10" s="46">
         <f>[2]EB1!U21</f>
         <v>325</v>
       </c>
-      <c r="V10" s="101">
+      <c r="V10" s="86">
         <f t="shared" si="0"/>
         <v>1411.5191499999987</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="56" t="s">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B11" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="98">
+      <c r="D11" s="83">
         <f>[2]EB1!D22</f>
         <v>34.094450000000002</v>
       </c>
-      <c r="E11" s="98">
+      <c r="E11" s="83">
         <f>[2]EB1!E22</f>
         <v>253.5292</v>
       </c>
-      <c r="F11" s="98">
+      <c r="F11" s="83">
         <f>[2]EB1!F22</f>
         <v>0</v>
       </c>
-      <c r="G11" s="98">
+      <c r="G11" s="83">
         <f>[2]EB1!G22</f>
         <v>76.465000000000003</v>
       </c>
-      <c r="H11" s="98">
+      <c r="H11" s="83">
         <f>[2]EB1!H22</f>
         <v>4.7945000000000002</v>
       </c>
-      <c r="I11" s="98">
+      <c r="I11" s="83">
         <f>[2]EB1!I22</f>
         <v>199.87350000000001</v>
       </c>
-      <c r="J11" s="98">
+      <c r="J11" s="83">
         <f>[2]EB1!J22</f>
         <v>3.1459999999999999</v>
       </c>
-      <c r="K11" s="98">
+      <c r="K11" s="83">
         <f>[2]EB1!K22</f>
         <v>899.20600000000002</v>
       </c>
-      <c r="L11" s="98">
+      <c r="L11" s="83">
         <f>[2]EB1!L22</f>
         <v>52.04</v>
       </c>
-      <c r="M11" s="98">
+      <c r="M11" s="83">
         <f>[2]EB1!M22</f>
         <v>800.72900000000004</v>
       </c>
-      <c r="N11" s="99">
+      <c r="N11" s="84">
         <f>[2]EB1!N22</f>
         <v>0</v>
       </c>
-      <c r="O11" s="98">
+      <c r="O11" s="83">
         <f>[2]EB1!O22</f>
         <v>0</v>
       </c>
-      <c r="P11" s="98">
+      <c r="P11" s="83">
         <f>[2]EB1!P22</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="98">
+      <c r="Q11" s="83">
         <f>[2]EB1!Q22</f>
         <v>0</v>
       </c>
-      <c r="R11" s="98">
+      <c r="R11" s="83">
         <f>[2]EB1!R22</f>
         <v>0</v>
       </c>
-      <c r="S11" s="98">
+      <c r="S11" s="83">
         <f>[2]EB1!S22</f>
         <v>0</v>
       </c>
-      <c r="T11" s="98">
+      <c r="T11" s="83">
         <f>[2]EB1!T22</f>
         <v>0</v>
       </c>
-      <c r="U11" s="98">
+      <c r="U11" s="83">
         <f>[2]EB1!U22</f>
         <v>0</v>
       </c>
-      <c r="V11" s="100">
+      <c r="V11" s="85">
         <f t="shared" si="0"/>
         <v>2323.8776500000004</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="56" t="s">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B12" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="98">
+      <c r="D12" s="83">
         <f>[2]EB1!D23</f>
         <v>0</v>
       </c>
-      <c r="E12" s="98">
+      <c r="E12" s="83">
         <f>[2]EB1!E23</f>
         <v>0</v>
       </c>
-      <c r="F12" s="98">
+      <c r="F12" s="83">
         <f>[2]EB1!F23</f>
         <v>0</v>
       </c>
-      <c r="G12" s="98">
+      <c r="G12" s="83">
         <f>[2]EB1!G23</f>
         <v>146.90600000000001</v>
       </c>
-      <c r="H12" s="98">
+      <c r="H12" s="83">
         <f>[2]EB1!H23</f>
         <v>0</v>
       </c>
-      <c r="I12" s="98">
+      <c r="I12" s="83">
         <f>[2]EB1!I23</f>
         <v>0</v>
       </c>
-      <c r="J12" s="98">
+      <c r="J12" s="83">
         <f>[2]EB1!J23</f>
         <v>0</v>
       </c>
-      <c r="K12" s="98">
+      <c r="K12" s="83">
         <f>[2]EB1!K23</f>
         <v>0</v>
       </c>
-      <c r="L12" s="98">
+      <c r="L12" s="83">
         <f>[2]EB1!L23</f>
         <v>902.14</v>
       </c>
-      <c r="M12" s="98">
+      <c r="M12" s="83">
         <f>[2]EB1!M23</f>
         <v>6.5</v>
       </c>
-      <c r="N12" s="99">
+      <c r="N12" s="84">
         <f>[2]EB1!N23</f>
         <v>0</v>
       </c>
-      <c r="O12" s="59">
+      <c r="O12" s="46">
         <f>[2]EB1!O23</f>
         <v>0</v>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="46">
         <f>[2]EB1!P23</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="59">
+      <c r="Q12" s="46">
         <f>[2]EB1!Q23</f>
         <v>0</v>
       </c>
-      <c r="R12" s="59">
+      <c r="R12" s="46">
         <f>[2]EB1!R23</f>
         <v>0</v>
       </c>
-      <c r="S12" s="98">
+      <c r="S12" s="83">
         <f>[2]EB1!S23</f>
         <v>0</v>
       </c>
-      <c r="T12" s="98">
+      <c r="T12" s="83">
         <f>[2]EB1!T23</f>
         <v>0</v>
       </c>
-      <c r="U12" s="98">
+      <c r="U12" s="83">
         <f>[2]EB1!U23</f>
         <v>0</v>
       </c>
-      <c r="V12" s="100">
+      <c r="V12" s="85">
         <f t="shared" si="0"/>
         <v>1055.546</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="95" t="s">
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="48">
         <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
         <v>2337.9238999999989</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="48">
         <f t="shared" si="1"/>
         <v>4881.9848000000002</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="48">
         <f t="shared" si="1"/>
         <v>5975.8215</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="48">
         <f t="shared" si="1"/>
         <v>1163.9024999999999</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="48">
         <f t="shared" si="1"/>
         <v>675.02300000000002</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="48">
         <f t="shared" si="1"/>
         <v>2415.732</v>
       </c>
-      <c r="K13" s="61">
+      <c r="K13" s="48">
         <f t="shared" si="1"/>
         <v>943.27200000000005</v>
       </c>
-      <c r="L13" s="61">
+      <c r="L13" s="48">
         <f t="shared" si="1"/>
         <v>1321.9105</v>
       </c>
-      <c r="M13" s="61">
+      <c r="M13" s="48">
         <f t="shared" si="1"/>
         <v>999.96400000000006</v>
       </c>
-      <c r="N13" s="61">
+      <c r="N13" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="48">
         <f t="shared" si="1"/>
         <v>1643.7629999999999</v>
       </c>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61">
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48">
         <f t="shared" si="1"/>
         <v>59.204999999999998</v>
       </c>
-      <c r="T13" s="61">
+      <c r="T13" s="48">
         <f t="shared" si="1"/>
         <v>1198.163</v>
       </c>
-      <c r="U13" s="61">
+      <c r="U13" s="48">
         <f>SUM(U5:U12)</f>
         <v>5211.4674999999997</v>
       </c>
-      <c r="V13" s="62">
+      <c r="V13" s="49">
         <f t="shared" si="1"/>
         <v>28885.632699999998</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="D14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="D15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="C16" s="60" t="s">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="C16" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="D17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="D18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="D19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="D20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="D21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="D22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-    </row>
-    <row r="24" spans="1:24" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="28" t="s">
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C23" s="1"/>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" spans="2:24" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="127" t="s">
+      <c r="D24" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="128" t="s">
+      <c r="E24" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="128" t="s">
+      <c r="F24" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="128" t="s">
+      <c r="G24" s="109" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="128" t="s">
+      <c r="H24" s="109" t="s">
         <v>138</v>
       </c>
-      <c r="I24" s="128" t="s">
+      <c r="I24" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="J24" s="128" t="s">
+      <c r="J24" s="109" t="s">
         <v>139</v>
       </c>
-      <c r="K24" s="128" t="s">
+      <c r="K24" s="109" t="s">
         <v>140</v>
       </c>
-      <c r="L24" s="128" t="s">
+      <c r="L24" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="M24" s="128" t="s">
+      <c r="M24" s="109" t="s">
         <v>137</v>
       </c>
-      <c r="N24" s="128" t="s">
+      <c r="N24" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="O24" s="128" t="s">
+      <c r="O24" s="109" t="s">
         <v>171</v>
       </c>
-      <c r="P24" s="128" t="s">
+      <c r="P24" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="Q24" s="128" t="s">
+      <c r="Q24" s="109" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="128" t="s">
+      <c r="R24" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="S24" s="128" t="s">
+      <c r="S24" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="T24" s="128" t="s">
+      <c r="T24" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="U24" s="129" t="s">
+      <c r="U24" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="V24" s="55" t="s">
+      <c r="V24" s="42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="105" t="s">
+    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="B25" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="110">
+      <c r="D25" s="90"/>
+      <c r="E25" s="94">
         <v>1</v>
       </c>
-      <c r="F25" s="107"/>
-      <c r="G25" s="110">
+      <c r="F25" s="91"/>
+      <c r="G25" s="94">
         <v>0.9</v>
       </c>
-      <c r="H25" s="107"/>
-      <c r="I25" s="110">
+      <c r="H25" s="91"/>
+      <c r="I25" s="94">
         <v>1</v>
       </c>
-      <c r="J25" s="110">
+      <c r="J25" s="94">
         <v>1</v>
       </c>
-      <c r="K25" s="107"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="110">
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="94">
         <v>0.75</v>
       </c>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="107"/>
-      <c r="R25" s="107"/>
-      <c r="S25" s="107"/>
-      <c r="T25" s="107"/>
-      <c r="U25" s="111">
-        <v>0</v>
-      </c>
-      <c r="V25" s="68"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="64" t="s">
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="91"/>
+      <c r="S25" s="91"/>
+      <c r="T25" s="91"/>
+      <c r="U25" s="95">
+        <v>0</v>
+      </c>
+      <c r="V25" s="55"/>
+      <c r="X25" s="51" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="105" t="s">
+    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="B26" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="108"/>
-      <c r="E26" s="112">
+      <c r="D26" s="92"/>
+      <c r="E26" s="96">
         <f>1-E25</f>
         <v>0</v>
       </c>
-      <c r="F26" s="109"/>
-      <c r="G26" s="112">
+      <c r="F26" s="93"/>
+      <c r="G26" s="96">
         <f>1-G25</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="H26" s="109"/>
-      <c r="I26" s="112">
+      <c r="H26" s="93"/>
+      <c r="I26" s="96">
         <f>1-I25</f>
         <v>0</v>
       </c>
-      <c r="J26" s="112">
+      <c r="J26" s="96">
         <f>1-J25</f>
         <v>0</v>
       </c>
-      <c r="K26" s="109"/>
-      <c r="L26" s="109"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="109"/>
-      <c r="O26" s="112">
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="93"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="96">
         <f>1-O25</f>
         <v>0.25</v>
       </c>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="109"/>
-      <c r="R26" s="109"/>
-      <c r="S26" s="109"/>
-      <c r="T26" s="109"/>
-      <c r="U26" s="113">
+      <c r="P26" s="93"/>
+      <c r="Q26" s="93"/>
+      <c r="R26" s="93"/>
+      <c r="S26" s="93"/>
+      <c r="T26" s="93"/>
+      <c r="U26" s="97">
         <f>1-U25</f>
         <v>1</v>
       </c>
-      <c r="V26" s="57"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="66" t="s">
+      <c r="V26" s="44"/>
+      <c r="X26" s="53" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="V27" s="8"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="V28" s="8"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="C29" s="71" t="s">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C29" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="V29" s="8"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="24" t="s">
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B30" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="103" t="s">
+      <c r="C30" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="103" t="s">
+      <c r="D30" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="89" t="s">
         <v>108</v>
       </c>
-      <c r="V30" s="8"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="56" t="s">
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B31" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="130">
+      <c r="C31" s="111">
         <v>1</v>
       </c>
-      <c r="D31" s="131"/>
-      <c r="E31" s="132"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="113"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6143,7 +6083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6153,17 +6093,17 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="71" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6173,7 +6113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R36"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6198,296 +6138,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="43"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="str">
+      <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
       </c>
-      <c r="C2" s="14" t="str">
+      <c r="C2" s="10" t="str">
         <f>'EB1'!C9</f>
         <v>Transport</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="10" t="str">
         <f>'EB1'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="10" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="J2" s="135" t="s">
+      <c r="H2" s="9"/>
+      <c r="J2" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="135"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="J3" s="137" t="s">
+      <c r="J3" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="138" t="s">
+      <c r="K3" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="137" t="s">
+      <c r="L3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="137" t="s">
+      <c r="N3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="137" t="s">
+      <c r="O3" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="137" t="s">
+      <c r="P3" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="137" t="s">
+      <c r="Q3" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="137" t="s">
+      <c r="R3" s="118" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="J4" s="139" t="s">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="J4" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="139" t="s">
+      <c r="K4" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="139" t="s">
+      <c r="L4" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="139" t="s">
+      <c r="M4" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="139" t="s">
+      <c r="N4" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="139" t="s">
+      <c r="O4" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="139" t="s">
+      <c r="P4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="139" t="s">
+      <c r="Q4" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="139" t="s">
+      <c r="R4" s="120" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="15"/>
-      <c r="J5" s="140" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="11"/>
+      <c r="J5" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140" t="str">
+      <c r="K5" s="121"/>
+      <c r="L5" s="121" t="str">
         <f>$B$2&amp;'EB1'!$E$2</f>
         <v>TRAGAS</v>
       </c>
-      <c r="M5" s="141" t="str">
+      <c r="M5" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$E$3</f>
         <v>Transport Natural Gas</v>
       </c>
-      <c r="N5" s="140" t="str">
+      <c r="N5" s="121" t="str">
         <f t="shared" ref="N5:N10" si="0">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="121"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="15"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140" t="str">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="11"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121" t="str">
         <f>$B$2&amp;'EB1'!$G$2</f>
         <v>TRADSL</v>
       </c>
-      <c r="M6" s="141" t="str">
+      <c r="M6" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$G$3</f>
         <v>Transport Diesel oil</v>
       </c>
-      <c r="N6" s="140" t="str">
+      <c r="N6" s="121" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="140"/>
-      <c r="R6" s="140"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="15"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140" t="str">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="11"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121" t="str">
         <f>$B$2&amp;'EB1'!$I$2</f>
         <v>TRALPG</v>
       </c>
-      <c r="M7" s="141" t="str">
+      <c r="M7" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$I$3</f>
         <v>Transport LPG</v>
       </c>
-      <c r="N7" s="140" t="str">
+      <c r="N7" s="121" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="121"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="15"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140" t="str">
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="11"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121" t="str">
         <f>$B$2&amp;'EB1'!$J$2</f>
         <v>TRAGSL</v>
       </c>
-      <c r="M8" s="141" t="str">
+      <c r="M8" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$J$3</f>
         <v>Transport Motor spirit</v>
       </c>
-      <c r="N8" s="140" t="str">
+      <c r="N8" s="121" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="121"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="15"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140" t="str">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="11"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121" t="str">
         <f>$B$2&amp;'EB1'!$O$2</f>
         <v>TRABIO</v>
       </c>
-      <c r="M9" s="141" t="str">
+      <c r="M9" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!O3</f>
         <v>Transport Biofuels</v>
       </c>
-      <c r="N9" s="140" t="str">
+      <c r="N9" s="121" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O9" s="140"/>
-      <c r="P9" s="142"/>
-      <c r="Q9" s="142"/>
-      <c r="R9" s="142"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="15"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140" t="str">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="11"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121" t="str">
         <f>$B$2&amp;'EB1'!$U$2</f>
         <v>TRAELC</v>
       </c>
-      <c r="M10" s="141" t="str">
+      <c r="M10" s="122" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$U$3</f>
         <v>Transport Electricity</v>
       </c>
-      <c r="N10" s="140" t="str">
+      <c r="N10" s="121" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140" t="s">
+      <c r="O10" s="121"/>
+      <c r="P10" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140" t="s">
+      <c r="Q10" s="121"/>
+      <c r="R10" s="121" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L11" s="32"/>
-      <c r="M11" s="34"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="5" t="s">
@@ -6495,144 +6417,144 @@
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="J12" s="135" t="s">
+      <c r="J12" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="135"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="142"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="142"/>
-      <c r="Q12" s="142"/>
-      <c r="R12" s="142"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="121"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="88" t="s">
+      <c r="F13" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="88" t="s">
+      <c r="G13" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="88" t="s">
+      <c r="H13" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="137" t="s">
+      <c r="J13" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="138" t="s">
+      <c r="K13" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="137" t="s">
+      <c r="L13" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="137" t="s">
+      <c r="M13" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="137" t="s">
+      <c r="N13" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="137" t="s">
+      <c r="O13" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="137" t="s">
+      <c r="P13" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="Q13" s="137" t="s">
+      <c r="Q13" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="137" t="s">
+      <c r="R13" s="118" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="139" t="s">
+      <c r="J14" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="139" t="s">
+      <c r="K14" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="139" t="s">
+      <c r="L14" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="139" t="s">
+      <c r="M14" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="139" t="s">
+      <c r="N14" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="O14" s="139" t="s">
+      <c r="O14" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="139" t="s">
+      <c r="P14" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="Q14" s="139" t="s">
+      <c r="Q14" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="R14" s="139" t="s">
+      <c r="R14" s="120" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17" t="str">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="str">
         <f>E2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17" t="s">
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="139" t="s">
+      <c r="J15" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="K15" s="143"/>
-      <c r="L15" s="143"/>
-      <c r="M15" s="143"/>
-      <c r="N15" s="143"/>
-      <c r="O15" s="143"/>
-      <c r="P15" s="143"/>
-      <c r="Q15" s="143"/>
-      <c r="R15" s="143"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -6647,37 +6569,37 @@
         <f t="shared" ref="D16:D21" si="3">L5</f>
         <v>TRAGAS</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="78">
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="65">
         <v>1</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="66">
         <v>30</v>
       </c>
-      <c r="J16" s="144" t="s">
+      <c r="J16" s="117" t="s">
         <v>112</v>
       </c>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140" t="str">
+      <c r="K16" s="121"/>
+      <c r="L16" s="121" t="str">
         <f t="shared" ref="L16:L21" si="4">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-TRAGAS</v>
       </c>
-      <c r="M16" s="141" t="str">
+      <c r="M16" s="122" t="str">
         <f t="shared" ref="M16:M21" si="5">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Transport Natural Gas</v>
       </c>
-      <c r="N16" s="140" t="str">
+      <c r="N16" s="121" t="str">
         <f t="shared" ref="N16:N21" si="6">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O16" s="140" t="str">
+      <c r="O16" s="121" t="str">
         <f t="shared" ref="O16:O21" si="7">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="140"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121"/>
+      <c r="R16" s="121"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
@@ -6692,35 +6614,35 @@
         <f t="shared" si="3"/>
         <v>TRADSL</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="78">
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="65">
         <v>1</v>
       </c>
-      <c r="H17" s="79">
+      <c r="H17" s="66">
         <v>30</v>
       </c>
-      <c r="J17" s="144"/>
-      <c r="K17" s="140"/>
-      <c r="L17" s="140" t="str">
+      <c r="J17" s="117"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRADSL</v>
       </c>
-      <c r="M17" s="141" t="str">
+      <c r="M17" s="122" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Diesel oil</v>
       </c>
-      <c r="N17" s="140" t="str">
+      <c r="N17" s="121" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O17" s="140" t="str">
+      <c r="O17" s="121" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P17" s="140"/>
-      <c r="Q17" s="140"/>
-      <c r="R17" s="140"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -6735,35 +6657,35 @@
         <f t="shared" si="3"/>
         <v>TRALPG</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="78">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="65">
         <v>1</v>
       </c>
-      <c r="H18" s="79">
+      <c r="H18" s="66">
         <v>30</v>
       </c>
-      <c r="J18" s="140"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140" t="str">
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="121" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRALPG</v>
       </c>
-      <c r="M18" s="141" t="str">
+      <c r="M18" s="122" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport LPG</v>
       </c>
-      <c r="N18" s="140" t="str">
+      <c r="N18" s="121" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O18" s="140" t="str">
+      <c r="O18" s="121" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="140"/>
-      <c r="R18" s="140"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
@@ -6778,35 +6700,35 @@
         <f t="shared" si="3"/>
         <v>TRAGSL</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="78">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="65">
         <v>1</v>
       </c>
-      <c r="H19" s="79">
+      <c r="H19" s="66">
         <v>30</v>
       </c>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="140" t="str">
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="121" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRAGSL</v>
       </c>
-      <c r="M19" s="141" t="str">
+      <c r="M19" s="122" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Motor spirit</v>
       </c>
-      <c r="N19" s="140" t="str">
+      <c r="N19" s="121" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O19" s="140" t="str">
+      <c r="O19" s="121" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P19" s="140"/>
-      <c r="Q19" s="140"/>
-      <c r="R19" s="140"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="121"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -6821,35 +6743,35 @@
         <f t="shared" si="3"/>
         <v>TRABIO</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="78">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="65">
         <v>1</v>
       </c>
-      <c r="H20" s="79">
+      <c r="H20" s="66">
         <v>30</v>
       </c>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140" t="str">
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRABIO</v>
       </c>
-      <c r="M20" s="141" t="str">
+      <c r="M20" s="122" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Biofuels</v>
       </c>
-      <c r="N20" s="140" t="str">
+      <c r="N20" s="121" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O20" s="140" t="str">
+      <c r="O20" s="121" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="140"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="121"/>
+      <c r="R20" s="121"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
@@ -6864,208 +6786,135 @@
         <f t="shared" si="3"/>
         <v>TRAELC</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="78">
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="65">
         <v>1</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="66">
         <v>30</v>
       </c>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140" t="str">
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRAELC</v>
       </c>
-      <c r="M21" s="141" t="str">
+      <c r="M21" s="122" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Electricity</v>
       </c>
-      <c r="N21" s="140" t="str">
+      <c r="N21" s="121" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O21" s="140" t="str">
+      <c r="O21" s="121" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P21" s="140" t="s">
+      <c r="P21" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="Q21" s="140"/>
-      <c r="R21" s="140"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="15"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="11"/>
+      <c r="M22" s="19"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="15"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="11"/>
+      <c r="M23" s="19"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="31"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="15"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
+      <c r="B24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="11"/>
+      <c r="M24" s="19"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B25" s="31"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="15"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
+      <c r="B25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="11"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="M25" s="19"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B26" s="31"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="15"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="B26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="11"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="M26" s="19"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B27" s="31"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="15"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+      <c r="B27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="11"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="M27" s="19"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B28" s="31"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="15"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="6"/>
+      <c r="B28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="11"/>
+      <c r="M28" s="19"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B29" s="31"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="15"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
+      <c r="B29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="11"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B30" s="32"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="15"/>
+      <c r="B30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B31" s="32"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="15"/>
+      <c r="B31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="11"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="58"/>
+      <c r="B35" s="45"/>
       <c r="C35" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="77"/>
+      <c r="B36" s="64"/>
       <c r="C36" s="1" t="s">
         <v>160</v>
       </c>
@@ -7079,8 +6928,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:W32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7094,7 +6943,7 @@
     <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.85546875" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
     <col min="15" max="15" width="12.42578125" customWidth="1"/>
@@ -7109,205 +6958,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="43"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="str">
+      <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
       </c>
-      <c r="C2" s="14" t="str">
+      <c r="C2" s="10" t="str">
         <f>'EB1'!C9</f>
         <v>Transport</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="10" t="str">
         <f>'EB1'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="10" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="O2" s="135" t="s">
+      <c r="I2" s="9"/>
+      <c r="O2" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
-      <c r="U2" s="136"/>
-      <c r="V2" s="136"/>
-      <c r="W2" s="136"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="O3" s="137" t="s">
+      <c r="O3" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="138" t="s">
+      <c r="P3" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="137" t="s">
+      <c r="Q3" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="137" t="s">
+      <c r="S3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="137" t="s">
+      <c r="T3" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="137" t="s">
+      <c r="U3" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="137" t="s">
+      <c r="V3" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="137" t="s">
+      <c r="W3" s="118" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="L4" s="38"/>
-      <c r="O4" s="139" t="s">
+    <row r="4" spans="2:23" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="O4" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="139" t="s">
+      <c r="P4" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="Q4" s="139" t="s">
+      <c r="Q4" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="R4" s="139" t="s">
+      <c r="R4" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="139" t="s">
+      <c r="S4" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="139" t="s">
+      <c r="T4" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="U4" s="139" t="s">
+      <c r="U4" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="139" t="s">
+      <c r="V4" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="139" t="s">
+      <c r="W4" s="120" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:23" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="L5" s="38"/>
-      <c r="O5" s="144" t="s">
+    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="O5" s="117" t="s">
         <v>83</v>
       </c>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="144" t="str">
+      <c r="P5" s="121"/>
+      <c r="Q5" s="117" t="str">
         <f>LEFT($O$5,1)&amp;LEFT($B$2,1)&amp;'EB1'!$C$25</f>
         <v>DTCAR</v>
       </c>
-      <c r="R5" s="144" t="str">
+      <c r="R5" s="117" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$25</f>
         <v>Demand Transport Sector - Cars</v>
       </c>
-      <c r="S5" s="149" t="s">
+      <c r="S5" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T5" s="144"/>
-      <c r="U5" s="144"/>
-      <c r="V5" s="144"/>
-      <c r="W5" s="144"/>
-    </row>
-    <row r="6" spans="2:23" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="L6" s="38"/>
-      <c r="O6" s="144"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="144" t="str">
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="117"/>
+      <c r="W5" s="117"/>
+    </row>
+    <row r="6" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="117" t="str">
         <f>LEFT($O$5,1)&amp;LEFT($B$2,1)&amp;'EB1'!$C$26</f>
         <v>DTPUB</v>
       </c>
-      <c r="R6" s="144" t="str">
+      <c r="R6" s="117" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$26</f>
         <v>Demand Transport Sector - Pub</v>
       </c>
-      <c r="S6" s="149" t="s">
+      <c r="S6" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T6" s="144"/>
-      <c r="U6" s="144"/>
-      <c r="V6" s="144"/>
-      <c r="W6" s="144"/>
+      <c r="T6" s="117"/>
+      <c r="U6" s="117"/>
+      <c r="V6" s="117"/>
+      <c r="W6" s="117"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="O7" s="142" t="s">
+      <c r="O7" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142" t="str">
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121" t="str">
         <f>$B$2&amp;'EB1'!$C$29</f>
         <v>TRACO2</v>
       </c>
-      <c r="R7" s="142" t="str">
+      <c r="R7" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$30</f>
         <v>Transport Carbon dioxide</v>
       </c>
-      <c r="S7" s="142" t="str">
+      <c r="S7" s="121" t="str">
         <f>'EB1'!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="T7" s="142"/>
-      <c r="U7" s="142"/>
-      <c r="V7" s="142"/>
-      <c r="W7" s="142"/>
+      <c r="T7" s="121"/>
+      <c r="U7" s="121"/>
+      <c r="V7" s="121"/>
+      <c r="W7" s="121"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.2">
       <c r="D9" s="5" t="s">
@@ -7316,189 +7162,189 @@
       <c r="E9" s="5"/>
       <c r="G9" s="5"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="18"/>
-      <c r="O9" s="135" t="s">
+      <c r="J9" s="14"/>
+      <c r="O9" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="142"/>
-      <c r="R9" s="142"/>
-      <c r="S9" s="142"/>
-      <c r="T9" s="142"/>
-      <c r="U9" s="142"/>
-      <c r="V9" s="142"/>
-      <c r="W9" s="142"/>
+      <c r="P9" s="116"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
+      <c r="U9" s="121"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="121"/>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="E10" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="88" t="s">
+      <c r="F10" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="G10" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="88" t="s">
+      <c r="H10" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="88" t="s">
+      <c r="I10" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="88" t="s">
+      <c r="J10" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="88" t="s">
+      <c r="K10" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="42" t="s">
+      <c r="L10" s="25"/>
+      <c r="M10" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="O10" s="137" t="s">
+      <c r="O10" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="P10" s="138" t="s">
+      <c r="P10" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="137" t="s">
+      <c r="Q10" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="R10" s="137" t="s">
+      <c r="R10" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="S10" s="137" t="s">
+      <c r="S10" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="137" t="s">
+      <c r="T10" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="U10" s="137" t="s">
+      <c r="U10" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="V10" s="137" t="s">
+      <c r="V10" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="W10" s="137" t="s">
+      <c r="W10" s="118" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="102" t="s">
+      <c r="G11" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="102" t="s">
+      <c r="H11" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="133" t="s">
+      <c r="L11" s="32"/>
+      <c r="M11" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="139" t="s">
+      <c r="O11" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="P11" s="139" t="s">
+      <c r="P11" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="139" t="s">
+      <c r="Q11" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="139" t="s">
+      <c r="R11" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="139" t="s">
+      <c r="S11" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="139" t="s">
+      <c r="T11" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="U11" s="139" t="s">
+      <c r="U11" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="V11" s="139" t="s">
+      <c r="V11" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W11" s="139" t="s">
+      <c r="W11" s="120" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="17" t="str">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="13" t="str">
         <f>G2</f>
         <v>000_Units</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="92" t="s">
+      <c r="G12" s="77" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="90" t="s">
+      <c r="H12" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="I12" s="17" t="str">
+      <c r="I12" s="13" t="str">
         <f>$F$2&amp;"/"&amp;G2&amp;"a"</f>
         <v>M€2005/000_Unitsa</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="45"/>
-      <c r="M12" s="134" t="s">
+      <c r="L12" s="32"/>
+      <c r="M12" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="O12" s="139" t="s">
+      <c r="O12" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="120"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="120"/>
+      <c r="U12" s="120"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="120"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
@@ -7513,56 +7359,56 @@
         <f t="shared" ref="D13:D18" si="2">$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="63">
         <f>('EB1'!E$9*'EB1'!$E$25*F13/(K13*G13))*1.01</f>
         <v>233.01046285714281</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F13" s="45">
         <v>0.38</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="45">
         <v>14</v>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="67">
         <v>1.25</v>
       </c>
-      <c r="I13" s="80">
+      <c r="I13" s="67">
         <v>0.16</v>
       </c>
-      <c r="J13" s="58">
+      <c r="J13" s="45">
         <v>10</v>
       </c>
-      <c r="K13" s="83">
+      <c r="K13" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="29">
         <f>E13*G13*K13*H13</f>
         <v>4.0776830999999989</v>
       </c>
-      <c r="O13" s="144" t="s">
+      <c r="O13" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140" t="str">
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$E$2</f>
         <v>TCAREGAS</v>
       </c>
-      <c r="R13" s="141" t="str">
+      <c r="R13" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Natural Gas</v>
       </c>
-      <c r="S13" s="150" t="s">
+      <c r="S13" s="126" t="s">
         <v>183</v>
       </c>
-      <c r="T13" s="144" t="str">
+      <c r="T13" s="117" t="str">
         <f t="shared" ref="T13:T24" si="3">$G$2</f>
         <v>000_Units</v>
       </c>
-      <c r="U13" s="140"/>
-      <c r="V13" s="144" t="s">
+      <c r="U13" s="121"/>
+      <c r="V13" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W13" s="140"/>
+      <c r="W13" s="121"/>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -7577,54 +7423,54 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="63">
         <f>('EB1'!G$9*'EB1'!$G$25*F14/(K14*G14))*1.01</f>
         <v>87102.97230272727</v>
       </c>
-      <c r="F14" s="80">
+      <c r="F14" s="67">
         <v>0.41</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="62">
         <v>16.5</v>
       </c>
-      <c r="H14" s="80">
+      <c r="H14" s="67">
         <v>1.25</v>
       </c>
-      <c r="I14" s="80">
+      <c r="I14" s="67">
         <v>0.16</v>
       </c>
-      <c r="J14" s="58">
+      <c r="J14" s="45">
         <v>10</v>
       </c>
-      <c r="K14" s="83">
+      <c r="K14" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="29">
         <f t="shared" ref="M14:M22" si="4">E14*G14*K14*H14</f>
         <v>1796.4988037437502</v>
       </c>
-      <c r="O14" s="140"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="140" t="str">
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$G$2</f>
         <v>TCAREDSL</v>
       </c>
-      <c r="R14" s="141" t="str">
+      <c r="R14" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Diesel oil</v>
       </c>
-      <c r="S14" s="149" t="s">
+      <c r="S14" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T14" s="144" t="str">
+      <c r="T14" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U14" s="140"/>
-      <c r="V14" s="144" t="s">
+      <c r="U14" s="121"/>
+      <c r="V14" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W14" s="140"/>
+      <c r="W14" s="121"/>
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" t="str">
@@ -7639,54 +7485,54 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="63">
         <f>('EB1'!I$9*'EB1'!$I$25*F15/(K15*G15))*1.01</f>
         <v>2583.2755571428575</v>
       </c>
-      <c r="F15" s="80">
+      <c r="F15" s="67">
         <v>0.38</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="62">
         <v>14</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="67">
         <v>1.25</v>
       </c>
-      <c r="I15" s="84">
+      <c r="I15" s="68">
         <v>0.16</v>
       </c>
-      <c r="J15" s="58">
+      <c r="J15" s="45">
         <v>10</v>
       </c>
-      <c r="K15" s="83">
+      <c r="K15" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="29">
         <f t="shared" si="4"/>
         <v>45.207322250000004</v>
       </c>
-      <c r="O15" s="140"/>
-      <c r="P15" s="140"/>
-      <c r="Q15" s="140" t="str">
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$I$2</f>
         <v>TCARELPG</v>
       </c>
-      <c r="R15" s="141" t="str">
+      <c r="R15" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - LPG</v>
       </c>
-      <c r="S15" s="149" t="s">
+      <c r="S15" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T15" s="144" t="str">
+      <c r="T15" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U15" s="140"/>
-      <c r="V15" s="144" t="s">
+      <c r="U15" s="121"/>
+      <c r="V15" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W15" s="140"/>
+      <c r="W15" s="121"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -7701,56 +7547,56 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="63">
         <f>('EB1'!J$9*'EB1'!$J$25*F16/(K16*G16))*1.01</f>
         <v>84109.849043478273</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="68">
         <v>0.4</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="62">
         <v>11.5</v>
       </c>
-      <c r="H16" s="80">
+      <c r="H16" s="67">
         <v>1.25</v>
       </c>
-      <c r="I16" s="80">
+      <c r="I16" s="67">
         <v>0.15</v>
       </c>
-      <c r="J16" s="58">
+      <c r="J16" s="45">
         <v>10</v>
       </c>
-      <c r="K16" s="83">
+      <c r="K16" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="29">
         <f t="shared" si="4"/>
         <v>1209.07908</v>
       </c>
-      <c r="O16" s="140"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140" t="str">
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$J$2</f>
         <v>TCAREGSL</v>
       </c>
-      <c r="R16" s="145" t="str">
+      <c r="R16" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Motor spirit</v>
       </c>
-      <c r="S16" s="149" t="s">
+      <c r="S16" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T16" s="144" t="str">
+      <c r="T16" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U16" s="140"/>
-      <c r="V16" s="144" t="s">
+      <c r="U16" s="121"/>
+      <c r="V16" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W16" s="140"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W16" s="121"/>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>Q17</f>
         <v>TCAREBIO</v>
@@ -7763,119 +7609,119 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="63">
         <f>('EB1'!O$9*'EB1'!$O$25*F17/(K17*G17))*1.01</f>
         <v>3181.5</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="68">
         <v>0.4</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="62">
         <v>11.5</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="67">
         <v>1.25</v>
       </c>
-      <c r="I17" s="80">
+      <c r="I17" s="67">
         <v>0.15</v>
       </c>
-      <c r="J17" s="58">
+      <c r="J17" s="45">
         <v>10</v>
       </c>
-      <c r="K17" s="83">
+      <c r="K17" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="29">
         <f>E17*G17*K17*H17</f>
         <v>45.734062499999993</v>
       </c>
-      <c r="O17" s="140"/>
-      <c r="P17" s="140"/>
-      <c r="Q17" s="140" t="str">
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$O$2</f>
         <v>TCAREBIO</v>
       </c>
-      <c r="R17" s="145" t="str">
+      <c r="R17" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!O3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Biofuels</v>
       </c>
-      <c r="S17" s="149" t="s">
+      <c r="S17" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T17" s="144" t="str">
+      <c r="T17" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U17" s="140"/>
-      <c r="V17" s="144" t="s">
+      <c r="U17" s="121"/>
+      <c r="V17" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W17" s="140"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B18" s="27" t="str">
+      <c r="W17" s="121"/>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TCAREELC</v>
       </c>
-      <c r="C18" s="27" t="str">
+      <c r="C18" s="6" t="str">
         <f t="shared" si="1"/>
         <v>TRAELC</v>
       </c>
-      <c r="D18" s="27" t="str">
+      <c r="D18" s="6" t="str">
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E18" s="94">
+      <c r="E18" s="79">
         <f>('EB1'!U$9*'EB1'!$U$25*F18/(K18*G18))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F18" s="115">
+      <c r="F18" s="99">
         <v>0.4</v>
       </c>
-      <c r="G18" s="116">
+      <c r="G18" s="100">
         <v>11.5</v>
       </c>
-      <c r="H18" s="117">
+      <c r="H18" s="101">
         <v>1.25</v>
       </c>
-      <c r="I18" s="117">
+      <c r="I18" s="101">
         <v>0.15</v>
       </c>
-      <c r="J18" s="118">
+      <c r="J18" s="102">
         <v>10</v>
       </c>
-      <c r="K18" s="119">
+      <c r="K18" s="103">
         <v>1E-3</v>
       </c>
-      <c r="L18" s="120"/>
-      <c r="M18" s="121">
+      <c r="L18" s="6"/>
+      <c r="M18" s="104">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O18" s="146"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="146" t="str">
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$25&amp;$H$2&amp;'EB1'!$U$2</f>
         <v>TCAREELC</v>
       </c>
-      <c r="R18" s="147" t="str">
+      <c r="R18" s="124" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Electricity</v>
       </c>
-      <c r="S18" s="148" t="s">
+      <c r="S18" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="T18" s="148" t="str">
+      <c r="T18" s="125" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U18" s="146"/>
-      <c r="V18" s="148" t="s">
+      <c r="U18" s="124"/>
+      <c r="V18" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="W18" s="146"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W18" s="124"/>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGAS</v>
@@ -7888,56 +7734,56 @@
         <f t="shared" ref="D19:D24" si="5">$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="63">
         <f>('EB1'!E$9*'EB1'!$E$26*F19/(K19*G19))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F19" s="80">
+      <c r="F19" s="67">
         <v>0.1</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="45">
         <v>50</v>
       </c>
-      <c r="H19" s="80">
+      <c r="H19" s="67">
         <v>15</v>
       </c>
-      <c r="I19" s="125">
+      <c r="I19" s="107">
         <v>0.24</v>
       </c>
-      <c r="J19" s="58">
+      <c r="J19" s="45">
         <v>30</v>
       </c>
-      <c r="K19" s="83">
+      <c r="K19" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M19" s="42">
+      <c r="M19" s="29">
         <f>E19*G19*K19*H19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="140"/>
-      <c r="P19" s="140"/>
-      <c r="Q19" s="140" t="str">
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$E$2</f>
         <v>TPUBEGAS</v>
       </c>
-      <c r="R19" s="141" t="str">
+      <c r="R19" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Natural Gas</v>
       </c>
-      <c r="S19" s="149" t="s">
+      <c r="S19" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T19" s="144" t="str">
+      <c r="T19" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U19" s="140"/>
-      <c r="V19" s="144" t="s">
+      <c r="U19" s="121"/>
+      <c r="V19" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W19" s="140"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W19" s="121"/>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEDSL</v>
@@ -7950,56 +7796,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="63">
         <f>('EB1'!G$9*'EB1'!$G$26*F20/(K20*G20))*1.01</f>
         <v>1168.4545064999998</v>
       </c>
-      <c r="F20" s="80">
+      <c r="F20" s="67">
         <v>0.15</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="62">
         <v>50</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="67">
         <v>15</v>
       </c>
-      <c r="I20" s="126">
+      <c r="I20" s="67">
         <v>0.24</v>
       </c>
-      <c r="J20" s="58">
+      <c r="J20" s="45">
         <v>30</v>
       </c>
-      <c r="K20" s="83">
+      <c r="K20" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="29">
         <f>E20*G20*K20*H20</f>
         <v>876.34087987499981</v>
       </c>
-      <c r="O20" s="140"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="140" t="str">
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$G$2</f>
         <v>TPUBEDSL</v>
       </c>
-      <c r="R20" s="141" t="str">
+      <c r="R20" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Diesel oil</v>
       </c>
-      <c r="S20" s="149" t="s">
+      <c r="S20" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T20" s="144" t="str">
+      <c r="T20" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U20" s="140"/>
-      <c r="V20" s="144" t="s">
+      <c r="U20" s="121"/>
+      <c r="V20" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W20" s="140"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W20" s="121"/>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>TPUBELPG</v>
@@ -8012,56 +7858,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="63">
         <f>('EB1'!I$9*'EB1'!$I$26*F21/(K21*G21))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F21" s="80">
+      <c r="F21" s="67">
         <v>0.1</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="62">
         <v>50</v>
       </c>
-      <c r="H21" s="80">
+      <c r="H21" s="67">
         <v>15</v>
       </c>
-      <c r="I21" s="126">
+      <c r="I21" s="67">
         <v>0.24</v>
       </c>
-      <c r="J21" s="58">
+      <c r="J21" s="45">
         <v>30</v>
       </c>
-      <c r="K21" s="83">
+      <c r="K21" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M21" s="42">
+      <c r="M21" s="29">
         <f>E21*G21*K21*H21</f>
         <v>0</v>
       </c>
-      <c r="O21" s="140"/>
-      <c r="P21" s="140"/>
-      <c r="Q21" s="140" t="str">
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$I$2</f>
         <v>TPUBELPG</v>
       </c>
-      <c r="R21" s="141" t="str">
+      <c r="R21" s="122" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - LPG</v>
       </c>
-      <c r="S21" s="149" t="s">
+      <c r="S21" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T21" s="144" t="str">
+      <c r="T21" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U21" s="140"/>
-      <c r="V21" s="144" t="s">
+      <c r="U21" s="121"/>
+      <c r="V21" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W21" s="140"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W21" s="121"/>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGSL</v>
@@ -8074,56 +7920,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="63">
         <f>('EB1'!J$9*'EB1'!$J$26*F22/(K22*G22))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="68">
         <v>0.15</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="62">
         <v>20</v>
       </c>
-      <c r="H22" s="80">
+      <c r="H22" s="67">
         <v>15</v>
       </c>
-      <c r="I22" s="126">
+      <c r="I22" s="67">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J22" s="58">
+      <c r="J22" s="45">
         <v>30</v>
       </c>
-      <c r="K22" s="83">
+      <c r="K22" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M22" s="42">
+      <c r="M22" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O22" s="140"/>
-      <c r="P22" s="140"/>
-      <c r="Q22" s="140" t="str">
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$J$2</f>
         <v>TPUBEGSL</v>
       </c>
-      <c r="R22" s="145" t="str">
+      <c r="R22" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Motor spirit</v>
       </c>
-      <c r="S22" s="149" t="s">
+      <c r="S22" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T22" s="144" t="str">
+      <c r="T22" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U22" s="140"/>
-      <c r="V22" s="144" t="s">
+      <c r="U22" s="121"/>
+      <c r="V22" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W22" s="140"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W22" s="121"/>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" t="str">
         <f>Q23</f>
         <v>TPUBEBIO</v>
@@ -8136,184 +7982,153 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="63">
         <f>('EB1'!O$9*'EB1'!$O$26*F23/(K23*G23))*1.01</f>
         <v>228.67031249999999</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="68">
         <v>0.15</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="62">
         <v>20</v>
       </c>
-      <c r="H23" s="80">
+      <c r="H23" s="67">
         <v>15</v>
       </c>
-      <c r="I23" s="126">
+      <c r="I23" s="67">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J23" s="58">
+      <c r="J23" s="45">
         <v>30</v>
       </c>
-      <c r="K23" s="83">
+      <c r="K23" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="29">
         <f>E23*G23*K23*H23</f>
         <v>68.60109374999999</v>
       </c>
-      <c r="O23" s="140"/>
-      <c r="P23" s="140"/>
-      <c r="Q23" s="140" t="str">
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="121" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$O$2</f>
         <v>TPUBEBIO</v>
       </c>
-      <c r="R23" s="145" t="str">
+      <c r="R23" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!O3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Biofuels</v>
       </c>
-      <c r="S23" s="149" t="s">
+      <c r="S23" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="T23" s="144" t="str">
+      <c r="T23" s="117" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U23" s="140"/>
-      <c r="V23" s="144" t="s">
+      <c r="U23" s="121"/>
+      <c r="V23" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="W23" s="140"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B24" s="27" t="str">
+      <c r="W23" s="121"/>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEELC</v>
       </c>
-      <c r="C24" s="27" t="str">
+      <c r="C24" s="6" t="str">
         <f t="shared" si="1"/>
         <v>TRAELC</v>
       </c>
-      <c r="D24" s="27" t="str">
+      <c r="D24" s="6" t="str">
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E24" s="94">
+      <c r="E24" s="79">
         <f>('EB1'!U$9*'EB1'!$U$26*F24/(K24*G24))*1.01</f>
         <v>40.294757999999995</v>
       </c>
-      <c r="F24" s="115">
+      <c r="F24" s="99">
         <v>0.03</v>
       </c>
-      <c r="G24" s="116">
+      <c r="G24" s="100">
         <v>100</v>
       </c>
-      <c r="H24" s="117">
+      <c r="H24" s="101">
         <v>200</v>
       </c>
-      <c r="I24" s="117">
+      <c r="I24" s="101">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J24" s="118">
+      <c r="J24" s="102">
         <v>30</v>
       </c>
-      <c r="K24" s="119">
+      <c r="K24" s="103">
         <v>1E-3</v>
       </c>
-      <c r="M24" s="121">
+      <c r="M24" s="104">
         <f>E24*G24*K24*H24</f>
         <v>805.89515999999981</v>
       </c>
-      <c r="O24" s="146"/>
-      <c r="P24" s="146"/>
-      <c r="Q24" s="146" t="str">
+      <c r="O24" s="124"/>
+      <c r="P24" s="124"/>
+      <c r="Q24" s="124" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$26&amp;$H$2&amp;'EB1'!$U$2</f>
         <v>TPUBEELC</v>
       </c>
-      <c r="R24" s="147" t="str">
+      <c r="R24" s="124" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Electricity</v>
       </c>
-      <c r="S24" s="148" t="s">
+      <c r="S24" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="T24" s="148" t="str">
+      <c r="T24" s="125" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U24" s="146"/>
-      <c r="V24" s="148" t="s">
+      <c r="U24" s="124"/>
+      <c r="V24" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="W24" s="146"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B27" s="58"/>
+      <c r="W24" s="124"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B27" s="45"/>
       <c r="C27" s="1" t="s">
         <v>159</v>
       </c>
       <c r="K27" s="1"/>
-      <c r="L27" s="11"/>
+      <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B28" s="77"/>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B28" s="64"/>
       <c r="C28" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K28" s="1"/>
-      <c r="L28" s="11"/>
+      <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
-      <c r="L29" s="11"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
-      <c r="L30" s="11"/>
+      <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E32" s="1"/>
     </row>
   </sheetData>
@@ -8324,7 +8139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:J24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8340,33 +8155,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14" t="str">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="str">
         <f>DemTechs_TRA!S5</f>
         <v>BPkm</v>
       </c>
-      <c r="G2" s="14" t="str">
+      <c r="G2" s="10" t="str">
         <f>'EB1'!Y2</f>
         <v>M€2005</v>
       </c>
@@ -8392,7 +8207,7 @@
       <c r="D6" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="78">
         <v>2005</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -8409,99 +8224,99 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="17" t="str">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="13" t="str">
         <f>E2</f>
         <v>BPkm</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="82">
+      <c r="E9" s="62">
         <f>SUM(DemTechs_TRA!M13:M18)</f>
         <v>3100.5969515937504</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H9" s="8" t="str">
+      <c r="H9" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="J9" s="58">
+      <c r="J9" s="45">
         <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="82">
+      <c r="E10" s="62">
         <f>SUM(DemTechs_TRA!M19:M24)</f>
         <v>1750.8371336249998</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="8" t="str">
+      <c r="H10" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="J10" s="58">
+      <c r="J10" s="45">
         <v>0.25</v>
       </c>
     </row>
@@ -8509,46 +8324,46 @@
       <c r="G11" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="8" t="str">
+      <c r="H11" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="58">
+      <c r="J11" s="45">
         <v>0.25</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E12" s="36"/>
-      <c r="G12" s="40" t="s">
+      <c r="E12" s="26"/>
+      <c r="G12" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="27" t="str">
+      <c r="H12" s="6" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="J12" s="118">
+      <c r="J12" s="102">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E13" s="10"/>
+      <c r="E13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="8" t="str">
+      <c r="H13" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="J13" s="58">
+      <c r="J13" s="45">
         <v>0.25</v>
       </c>
     </row>
@@ -8556,30 +8371,30 @@
       <c r="G14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="8" t="str">
+      <c r="H14" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="58">
+      <c r="J14" s="45">
         <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E15" s="10"/>
+      <c r="E15" s="7"/>
       <c r="G15" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="8" t="str">
+      <c r="H15" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="58">
+      <c r="J15" s="45">
         <v>0.25</v>
       </c>
     </row>
@@ -8587,25 +8402,25 @@
       <c r="G16" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="8" t="str">
+      <c r="H16" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I16" s="122" t="s">
+      <c r="I16" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="58">
+      <c r="J16" s="45">
         <v>0.25</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="58"/>
+      <c r="B23" s="45"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="77"/>
+      <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
       </c>
@@ -8617,123 +8432,151 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B3:J28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
+    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-    </row>
-    <row r="4" spans="2:9" s="6" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-    </row>
-    <row r="5" spans="2:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="B5" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-    </row>
-    <row r="6" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="51" t="str">
+      <c r="C5" s="34"/>
+    </row>
+    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="38" t="str">
         <f>Sector_Fuels_TRA!L5</f>
         <v>TRAGAS</v>
       </c>
-      <c r="D6" s="51" t="str">
+      <c r="D6" s="38" t="str">
         <f>Sector_Fuels_TRA!L6</f>
         <v>TRADSL</v>
       </c>
-      <c r="E6" s="51" t="str">
+      <c r="E6" s="38" t="str">
         <f>Sector_Fuels_TRA!L7</f>
         <v>TRALPG</v>
       </c>
-      <c r="F6" s="51" t="str">
+      <c r="F6" s="38" t="str">
         <f>Sector_Fuels_TRA!L8</f>
         <v>TRAGSL</v>
       </c>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="50" t="str">
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="127" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="67">
         <v>56.1</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="67">
         <v>75</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="67">
         <v>64</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="67">
         <v>73</v>
       </c>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="58"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="J14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="45"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="77"/>
+      <c r="H23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>191</v>
+      </c>
+      <c r="I28" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/VT_REG1_TRA_V12.xlsx
+++ b/VT_REG1_TRA_V12.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CD18D5-2F23-4F57-878A-FB6AA4430DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="EB1" sheetId="133" r:id="rId1"/>
-    <sheet name="RES_TRA" sheetId="135" r:id="rId2"/>
-    <sheet name="Sector_Fuels_TRA" sheetId="152" r:id="rId3"/>
-    <sheet name="DemTechs_TRA" sheetId="141" r:id="rId4"/>
-    <sheet name="Demands" sheetId="134" r:id="rId5"/>
-    <sheet name="Emi" sheetId="149" r:id="rId6"/>
+    <sheet name="EB1" sheetId="133" r:id="rId3"/>
+    <sheet name="RES_TRA" sheetId="135" r:id="rId4"/>
+    <sheet name="Sector_Fuels_TRA" sheetId="152" r:id="rId5"/>
+    <sheet name="DemTechs_TRA" sheetId="141" r:id="rId6"/>
+    <sheet name="Demands" sheetId="134" r:id="rId7"/>
+    <sheet name="Emi" sheetId="149" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -55,746 +54,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t>Includes fisheries consumption</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Gary Goldstein</author>
-    <author>Amit Kanudia</author>
-    <author>Maurizio Gargiulo</author>
-  </authors>
-  <commentList>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
-Allowed Cset:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NRG</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Energy)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ENV</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Emission)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DEM</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>MAT</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Material)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>FIN</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Financial)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amit Kanudia:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LO for PRODUCTION &gt;= CONSUMPTION (Default)
-FX for PRODUCTION = CONSUMPTION
-UP for PRODUCTION &lt;= CONSUMPTION</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed CTSLvl</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed PeakTS</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ANNUAL </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for all the TimeSlices)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-User TS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for a single TS)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed Ctype
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ELC</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Electricity)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed TsLvl
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ANNUAL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Annual level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amit Kanudia:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Needed only when one wants to override the VEDA default assignment
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed Vintage</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-NO</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (if empty by default mean </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NO</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-YES</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sets declarations are </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>inherited. 
-Allowed Process Sets</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ELE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Thermal Electric Power Plant)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-CHP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Combined Heat and Power)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGTSS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pump Storage)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGIPS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Pump Storage IP)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-PRE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Genric Process/Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DMD</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand Device)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-IMP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(Import)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EXP</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Export)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-MIN </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Mining Process)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RNW </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Renewable Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-HPL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Heating Plant)</t>
         </r>
       </text>
     </comment>
@@ -810,12 +73,11 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -827,7 +89,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -836,7 +97,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -847,7 +107,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -856,7 +115,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -867,7 +125,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -876,7 +133,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -887,7 +143,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -896,7 +151,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -907,7 +161,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -916,7 +169,672 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Financial)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+LO for PRODUCTION &gt;= CONSUMPTION (Default)
+FX for PRODUCTION = CONSUMPTION
+UP for PRODUCTION &lt;= CONSUMPTION</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed CTSLvl</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed PeakTS</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ANNUAL </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for all the TimeSlices)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+User TS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for a single TS)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed Ctype
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ELC</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Electricity)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed TsLvl
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ANNUAL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Annual level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Needed only when one wants to override the VEDA default assignment
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed Vintage</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (if empty by default mean </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+YES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sets declarations are </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>inherited. 
+Allowed Process Sets</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ELE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Thermal Electric Power Plant)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CHP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Combined Heat and Power)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGTSS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pump Storage)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGIPS</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Pump Storage IP)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+PRE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Genric Process/Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DMD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand Device)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+IMP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Import)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EXP</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Export)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+MIN </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Mining Process)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RNW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Renewable Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+HPL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Heating Plant)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gary Goldstein</author>
+    <author>Amit Kanudia</author>
+    <author>Maurizio Gargiulo</author>
+  </authors>
+  <commentList>
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
+Allowed Cset:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NRG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Energy)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ENV</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Emission)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DEM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>MAT</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Material)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIN</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -930,7 +848,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -939,7 +856,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -955,7 +871,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -965,7 +880,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -975,7 +889,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -985,7 +898,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -995,7 +907,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1005,7 +916,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1015,7 +925,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1028,7 +937,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1038,7 +946,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1048,7 +955,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1058,7 +964,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1068,7 +973,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1081,7 +985,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1092,7 +995,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1101,7 +1003,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1114,7 +1015,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1125,7 +1025,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1134,7 +1033,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1145,7 +1043,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1154,7 +1051,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1165,7 +1061,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1174,7 +1069,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1185,7 +1079,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1194,7 +1087,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1208,7 +1100,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1217,7 +1108,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1232,7 +1122,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1242,7 +1131,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1252,7 +1140,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1262,7 +1149,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1271,7 +1157,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1281,7 +1166,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1295,7 +1179,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1304,7 +1187,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1315,7 +1197,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1325,7 +1206,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1335,7 +1215,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1345,7 +1224,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1355,7 +1233,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1365,7 +1242,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1375,7 +1251,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1385,7 +1260,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1395,7 +1269,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1405,7 +1278,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1415,7 +1287,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1425,7 +1296,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1435,7 +1305,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1445,7 +1314,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1456,7 +1324,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1465,7 +1332,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1475,7 +1341,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1485,7 +1350,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1495,7 +1359,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1505,7 +1368,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1515,7 +1377,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1525,7 +1386,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -2126,14 +1986,17 @@
     <numFmt numFmtId="166" formatCode="General_)"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2147,11 +2010,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="12"/>
@@ -2160,14 +2018,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -2184,23 +2040,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2275,15 +2120,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
-      <color theme="9" tint="-0.249977111117893"/>
+      <color theme="9" tint="-0.249970003962517"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2311,7 +2150,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2323,86 +2222,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2412,195 +2256,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2617,319 +2272,636 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
     </border>
   </borders>
-  <cellStyleXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="41">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="31" applyAlignment="1">
       <alignment horizontal="right"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="23"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="26" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="26" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="26" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="29">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="29" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="29" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="29" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="12" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="23" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="26" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="26" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="10" applyBorder="1"/>
-    <xf numFmtId="1" fontId="24" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="18" fillId="10" borderId="0" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="16" fillId="8" borderId="4" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="15" fillId="8" borderId="0" xfId="27" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="6" borderId="5" xfId="24" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="8" borderId="5" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="6" borderId="6" xfId="24" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="8" borderId="6" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="7" xfId="24" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="9" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="28" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="10" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="15" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="15" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="15" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="15" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="10" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="18" fillId="10" borderId="16" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="18" fillId="10" borderId="2" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="18" fillId="10" borderId="14" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="24" fillId="13" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="39" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="12" borderId="3" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="13" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="12" borderId="2" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="13" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="12" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="23">
-    <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
-    <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="3" builtinId="36"/>
-    <cellStyle name="Accent2" xfId="4" builtinId="33"/>
-    <cellStyle name="Calculation" xfId="5" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Good" xfId="7" builtinId="26"/>
-    <cellStyle name="Input" xfId="8" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="9" builtinId="28"/>
+  <cellStyles count="27">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Normal 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Normal 4" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Normal 8" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal 9 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Normale_B2020" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Percent" xfId="17" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Percent 3" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Percent 4" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Percent 5" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="20% - Accent5" xfId="20" builtinId="46"/>
+    <cellStyle name="40% - Accent3" xfId="21" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="22" builtinId="36"/>
+    <cellStyle name="Accent2" xfId="23" builtinId="33"/>
+    <cellStyle name="Calculation" xfId="24" builtinId="22"/>
+    <cellStyle name="Comma 2" xfId="25"/>
+    <cellStyle name="Good" xfId="26" builtinId="26"/>
+    <cellStyle name="Input" xfId="27" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="28" builtinId="28"/>
+    <cellStyle name="Normal 10" xfId="29"/>
+    <cellStyle name="Normal 2" xfId="30"/>
+    <cellStyle name="Normal 4" xfId="31"/>
+    <cellStyle name="Normal 4 2" xfId="32"/>
+    <cellStyle name="Normal 8" xfId="33"/>
+    <cellStyle name="Normal 9 2" xfId="34"/>
+    <cellStyle name="Normale_B2020" xfId="35"/>
+    <cellStyle name="Percent 2" xfId="36"/>
+    <cellStyle name="Percent 3" xfId="37"/>
+    <cellStyle name="Percent 4" xfId="38"/>
+    <cellStyle name="Percent 5" xfId="39"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="40"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2942,7 +2914,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -2956,12 +2928,12 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>150451</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{743ABD8A-4426-46DB-BCA6-04E5E9EE3061}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{743abd8a-4426-46db-bca6-04e5e9ee3061}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2969,12 +2941,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5133974" y="4802717"/>
-          <a:ext cx="4327525" cy="958850"/>
+          <a:off x="5800725" y="2857500"/>
+          <a:ext cx="4343400" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -2983,7 +2953,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -2991,32 +2961,45 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr/>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="1"/>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Column B</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100"/>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t> (rows</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t> 5 -24) is used to set up the technology and commoditiy names and descriptions in the model.</a:t>
           </a:r>
         </a:p>
@@ -3025,7 +3008,11 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Row 2 and Row 3 are used to build  techology and commodity names and descriptions in the model.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100"/>
@@ -3038,7 +3025,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3057,7 +3044,7 @@
         <xdr:cNvPr id="57161" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1155A37F-2001-49DB-BEE2-A8B250FFCB37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1155a37f-2001-49db-bee2-a8b250ffcb37}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3066,14 +3053,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3083,9 +3069,7 @@
           <a:off x="123825" y="895350"/>
           <a:ext cx="800100" cy="2238375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3131,7 +3115,7 @@
         <xdr:cNvPr id="57162" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A47E3F4E-F580-4E26-95BF-99AE0BF4AA23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a47e3f4e-f580-4e26-95bf-99ae0bf4aa23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3140,14 +3124,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3157,9 +3140,7 @@
           <a:off x="1095375" y="18859500"/>
           <a:ext cx="4029075" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3205,7 +3186,7 @@
         <xdr:cNvPr id="57163" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2838DB47-3FA6-434D-9325-E54A4DE3B1E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2838db47-3fa6-434d-9325-e54a4de3b1e4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3214,14 +3195,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3231,9 +3211,7 @@
           <a:off x="1095375" y="1038225"/>
           <a:ext cx="3114675" cy="3933825"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3279,7 +3257,7 @@
         <xdr:cNvPr id="57164" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3CF8021-41D1-41FD-B20A-075608644F0E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e3cf8021-41d1-41fd-b20a-075608644f0e}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3288,14 +3266,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3305,9 +3282,7 @@
           <a:off x="1095375" y="4972050"/>
           <a:ext cx="3114675" cy="3848100"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3339,7 +3314,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -3353,12 +3328,12 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B22A26E7-FCE3-4D13-8D7D-391825F2511D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b22a26e7-fce3-4d13-8d7d-391825f2511d}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3366,12 +3341,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6528435" y="5210175"/>
-          <a:ext cx="6461760" cy="981075"/>
+          <a:off x="6524625" y="5372100"/>
+          <a:ext cx="6457950" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3380,7 +3353,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3388,16 +3361,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3408,7 +3381,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3420,7 +3393,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3432,7 +3405,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3446,7 +3419,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3459,7 +3432,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3471,7 +3444,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3482,7 +3455,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3498,7 +3471,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
@@ -3512,12 +3485,12 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D0F848D-E838-455E-B3D6-869D4F0572D4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8d0f848d-e838-455e-b3d6-869d4f0572d4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3525,12 +3498,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9736666" y="4402667"/>
-          <a:ext cx="5886255" cy="1028700"/>
+          <a:off x="9877425" y="4933950"/>
+          <a:ext cx="5895975" cy="1047750"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3539,7 +3510,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3547,16 +3518,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3567,7 +3538,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3579,7 +3550,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3591,7 +3562,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3603,7 +3574,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3615,7 +3586,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3627,7 +3598,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3639,7 +3610,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3653,7 +3624,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3666,7 +3637,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3678,7 +3649,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3689,7 +3660,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3705,7 +3676,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3719,12 +3690,12 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F731CAED-5751-4DE0-9DBD-659456CABF21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f731caed-5751-4de0-9dbd-659456cabf21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3735,9 +3706,7 @@
           <a:off x="152400" y="2981325"/>
           <a:ext cx="3238500" cy="600075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3746,7 +3715,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3754,16 +3723,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3774,7 +3743,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3786,7 +3755,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3797,7 +3766,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3813,7 +3782,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3827,12 +3796,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B7A0C2-6705-4D77-8A9C-0A9AEC58235E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68b7a0c2-6705-4d77-8a9c-0a9aec58235e}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3840,12 +3809,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1971675"/>
+          <a:off x="609600" y="2143125"/>
           <a:ext cx="4391025" cy="552450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3854,7 +3821,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3862,16 +3829,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3882,7 +3849,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3894,7 +3861,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3905,7 +3872,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3921,7 +3888,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -4056,7 +4023,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -4072,7 +4039,7 @@
             <v>231.76075</v>
           </cell>
           <cell r="E16">
-            <v>2063.9171999999999</v>
+            <v>2063.9172</v>
           </cell>
           <cell r="G16">
             <v>862.053</v>
@@ -4081,10 +4048,10 @@
             <v>72.9495</v>
           </cell>
           <cell r="I16">
-            <v>190.17599999999999</v>
+            <v>190.176</v>
           </cell>
           <cell r="J16">
-            <v>3.1680000000000001</v>
+            <v>3.168</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -4099,7 +4066,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>895.44524999999999</v>
+            <v>895.44525</v>
           </cell>
           <cell r="P16">
             <v>0</v>
@@ -4114,21 +4081,21 @@
             <v>0</v>
           </cell>
           <cell r="T16">
-            <v>432.74250000000001</v>
+            <v>432.7425</v>
           </cell>
           <cell r="U16">
-            <v>1435.8710000000001</v>
+            <v>1435.871</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>37.001249999999999</v>
+            <v>37.00125</v>
           </cell>
           <cell r="E17">
-            <v>700.69200000000001</v>
+            <v>700.692</v>
           </cell>
           <cell r="G17">
-            <v>368.84399999999999</v>
+            <v>368.844</v>
           </cell>
           <cell r="H17">
             <v>1.677</v>
@@ -4146,7 +4113,7 @@
             <v>19.32</v>
           </cell>
           <cell r="M17">
-            <v>0.24199999999999999</v>
+            <v>0.242</v>
           </cell>
           <cell r="N17">
             <v>0</v>
@@ -4164,10 +4131,10 @@
             <v>7.5</v>
           </cell>
           <cell r="S17">
-            <v>0.60850000000000004</v>
+            <v>0.6085</v>
           </cell>
           <cell r="T17">
-            <v>127.32299999999999</v>
+            <v>127.323</v>
           </cell>
           <cell r="U17">
             <v>1263.6955</v>
@@ -4175,37 +4142,37 @@
         </row>
         <row r="18">
           <cell r="D18">
-            <v>1233.0409000000002</v>
+            <v>1233.0409</v>
           </cell>
           <cell r="E18">
-            <v>1774.8644000000002</v>
+            <v>1774.8644</v>
           </cell>
           <cell r="G18">
             <v>298.68</v>
           </cell>
           <cell r="H18">
-            <v>36.356499999999997</v>
+            <v>36.3565</v>
           </cell>
           <cell r="I18">
-            <v>142.97149999999999</v>
+            <v>142.9715</v>
           </cell>
           <cell r="J18">
             <v>7.766</v>
           </cell>
           <cell r="K18">
-            <v>44.066000000000003</v>
+            <v>44.066</v>
           </cell>
           <cell r="L18">
             <v>286.0505</v>
           </cell>
           <cell r="M18">
-            <v>191.57300000000001</v>
+            <v>191.573</v>
           </cell>
           <cell r="N18">
             <v>0</v>
           </cell>
           <cell r="O18">
-            <v>541.25324999999998</v>
+            <v>541.25325</v>
           </cell>
           <cell r="P18">
             <v>0</v>
@@ -4217,27 +4184,21 @@
             <v>0</v>
           </cell>
           <cell r="S18">
-            <v>58.595999999999997</v>
+            <v>58.596</v>
           </cell>
           <cell r="T18">
-            <v>316.79149999999998</v>
+            <v>316.7915</v>
           </cell>
           <cell r="U18">
             <v>2044.222</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="D19">
-            <v>28.665000000000003</v>
-          </cell>
-          <cell r="E19">
-            <v>80.482399999999998</v>
-          </cell>
           <cell r="G19">
-            <v>366.58800000000002</v>
+            <v>366.588</v>
           </cell>
           <cell r="H19">
-            <v>0.47299999999999998</v>
+            <v>0.473</v>
           </cell>
           <cell r="I19">
             <v>16.169</v>
@@ -4258,7 +4219,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>47.314499999999995</v>
+            <v>47.3145</v>
           </cell>
           <cell r="P19">
             <v>0</v>
@@ -4270,21 +4231,21 @@
             <v>0</v>
           </cell>
           <cell r="S19">
-            <v>5.0000000000000001E-4</v>
+            <v>0.0005</v>
           </cell>
           <cell r="T19">
-            <v>7.7869999999999999</v>
+            <v>7.787</v>
           </cell>
           <cell r="U19">
-            <v>9.6930000000000014</v>
+            <v>9.693</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>0.36140000000000005</v>
+            <v>0.3614</v>
           </cell>
           <cell r="E20">
-            <v>8.4995999999999992</v>
+            <v>8.4996</v>
           </cell>
           <cell r="G20">
             <v>3856.2855</v>
@@ -4293,10 +4254,10 @@
             <v>1047.652</v>
           </cell>
           <cell r="I20">
-            <v>94.230999999999995</v>
+            <v>94.231</v>
           </cell>
           <cell r="J20">
-            <v>2394.2159999999999</v>
+            <v>2394.216</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -4329,12 +4290,12 @@
             <v>0</v>
           </cell>
           <cell r="U20">
-            <v>132.98599999999999</v>
+            <v>132.986</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>773.00014999999871</v>
+            <v>773.000149999999</v>
           </cell>
           <cell r="E21">
             <v>0</v>
@@ -4379,7 +4340,7 @@
             <v>0</v>
           </cell>
           <cell r="T21">
-            <v>313.51900000000001</v>
+            <v>313.519</v>
           </cell>
           <cell r="U21">
             <v>325</v>
@@ -4387,31 +4348,31 @@
         </row>
         <row r="22">
           <cell r="D22">
-            <v>34.094450000000002</v>
+            <v>34.09445</v>
           </cell>
           <cell r="E22">
             <v>253.5292</v>
           </cell>
           <cell r="G22">
-            <v>76.465000000000003</v>
+            <v>76.465</v>
           </cell>
           <cell r="H22">
-            <v>4.7945000000000002</v>
+            <v>4.7945</v>
           </cell>
           <cell r="I22">
-            <v>199.87350000000001</v>
+            <v>199.8735</v>
           </cell>
           <cell r="J22">
-            <v>3.1459999999999999</v>
+            <v>3.146</v>
           </cell>
           <cell r="K22">
-            <v>899.20600000000002</v>
+            <v>899.206</v>
           </cell>
           <cell r="L22">
             <v>52.04</v>
           </cell>
           <cell r="M22">
-            <v>800.72900000000004</v>
+            <v>800.729</v>
           </cell>
           <cell r="N22">
             <v>0</v>
@@ -4446,7 +4407,7 @@
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>146.90600000000001</v>
+            <v>146.906</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -4846,23 +4807,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA31"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
-    <col min="4" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.2857142857143" customWidth="1"/>
+    <col min="4" max="21" width="10.8571428571429" customWidth="1"/>
+    <col min="22" max="22" width="7.28571428571429" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28571428571429" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="24:27" ht="12.75">
       <c r="X1" s="20" t="s">
         <v>93</v>
       </c>
@@ -4876,7 +4837,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:27" ht="15.75">
       <c r="D2" s="41" t="s">
         <v>44</v>
       </c>
@@ -4944,7 +4905,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:22" ht="38.25">
       <c r="C3" s="61" t="s">
         <v>126</v>
       </c>
@@ -5006,7 +4967,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" ht="12.75">
       <c r="B4" s="39"/>
       <c r="C4" s="81" t="s">
         <v>57</v>
@@ -5031,7 +4992,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="82"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:22" ht="12.75">
       <c r="B5" s="43" t="s">
         <v>58</v>
       </c>
@@ -5039,75 +5000,75 @@
         <v>59</v>
       </c>
       <c r="D5" s="83">
-        <f>[2]EB1!D16</f>
+        <f>'[2]EB1'!D16</f>
         <v>231.76075</v>
       </c>
       <c r="E5" s="83">
-        <f>[2]EB1!E16</f>
+        <f>'[2]EB1'!E16</f>
         <v>2063.9171999999999</v>
       </c>
       <c r="F5" s="83">
-        <f>[2]EB1!F16</f>
+        <f>'[2]EB1'!F16</f>
         <v>0</v>
       </c>
       <c r="G5" s="83">
-        <f>[2]EB1!G16</f>
+        <f>'[2]EB1'!G16</f>
         <v>862.053</v>
       </c>
       <c r="H5" s="83">
-        <f>[2]EB1!H16</f>
+        <f>'[2]EB1'!H16</f>
         <v>72.9495</v>
       </c>
       <c r="I5" s="83">
-        <f>[2]EB1!I16</f>
+        <f>'[2]EB1'!I16</f>
         <v>190.17599999999999</v>
       </c>
       <c r="J5" s="83">
-        <f>[2]EB1!J16</f>
+        <f>'[2]EB1'!J16</f>
         <v>3.1680000000000001</v>
       </c>
       <c r="K5" s="83">
-        <f>[2]EB1!K16</f>
+        <f>'[2]EB1'!K16</f>
         <v>0</v>
       </c>
       <c r="L5" s="83">
-        <f>[2]EB1!L16</f>
-        <v>15.38</v>
+        <f>'[2]EB1'!L16</f>
+        <v>15.380000000000001</v>
       </c>
       <c r="M5" s="83">
-        <f>[2]EB1!M16</f>
-        <v>0.92</v>
+        <f>'[2]EB1'!M16</f>
+        <v>0.92000000000000004</v>
       </c>
       <c r="N5" s="84">
-        <f>[2]EB1!N16</f>
+        <f>'[2]EB1'!N16</f>
         <v>0</v>
       </c>
       <c r="O5" s="83">
-        <f>[2]EB1!O16</f>
+        <f>'[2]EB1'!O16</f>
         <v>895.44524999999999</v>
       </c>
       <c r="P5" s="83">
-        <f>[2]EB1!P16</f>
+        <f>'[2]EB1'!P16</f>
         <v>0</v>
       </c>
       <c r="Q5" s="83">
-        <f>[2]EB1!Q16</f>
+        <f>'[2]EB1'!Q16</f>
         <v>0</v>
       </c>
       <c r="R5" s="83">
-        <f>[2]EB1!R16</f>
+        <f>'[2]EB1'!R16</f>
         <v>50</v>
       </c>
       <c r="S5" s="83">
-        <f>[2]EB1!S16</f>
+        <f>'[2]EB1'!S16</f>
         <v>0</v>
       </c>
       <c r="T5" s="83">
-        <f>[2]EB1!T16</f>
+        <f>'[2]EB1'!T16</f>
         <v>432.74250000000001</v>
       </c>
       <c r="U5" s="83">
-        <f>[2]EB1!U16</f>
+        <f>'[2]EB1'!U16</f>
         <v>1435.8710000000001</v>
       </c>
       <c r="V5" s="85">
@@ -5115,7 +5076,7 @@
         <v>6254.3832000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:22" ht="12.75">
       <c r="B6" s="43" t="s">
         <v>60</v>
       </c>
@@ -5123,83 +5084,83 @@
         <v>61</v>
       </c>
       <c r="D6" s="83">
-        <f>[2]EB1!D17</f>
+        <f>'[2]EB1'!D17</f>
         <v>37.001249999999999</v>
       </c>
       <c r="E6" s="83">
-        <f>[2]EB1!E17</f>
+        <f>'[2]EB1'!E17</f>
         <v>700.69200000000001</v>
       </c>
       <c r="F6" s="83">
-        <f>[2]EB1!F17</f>
+        <f>'[2]EB1'!F17</f>
         <v>0</v>
       </c>
       <c r="G6" s="83">
-        <f>[2]EB1!G17</f>
+        <f>'[2]EB1'!G17</f>
         <v>368.84399999999999</v>
       </c>
       <c r="H6" s="83">
-        <f>[2]EB1!H17</f>
+        <f>'[2]EB1'!H17</f>
         <v>1.677</v>
       </c>
       <c r="I6" s="83">
-        <f>[2]EB1!I17</f>
+        <f>'[2]EB1'!I17</f>
         <v>31.602</v>
       </c>
       <c r="J6" s="83">
-        <f>[2]EB1!J17</f>
-        <v>5.72</v>
+        <f>'[2]EB1'!J17</f>
+        <v>5.7199999999999998</v>
       </c>
       <c r="K6" s="83">
-        <f>[2]EB1!K17</f>
+        <f>'[2]EB1'!K17</f>
         <v>0</v>
       </c>
       <c r="L6" s="83">
-        <f>[2]EB1!L17</f>
+        <f>'[2]EB1'!L17</f>
         <v>19.32</v>
       </c>
       <c r="M6" s="83">
-        <f>[2]EB1!M17</f>
+        <f>'[2]EB1'!M17</f>
         <v>0.24199999999999999</v>
       </c>
       <c r="N6" s="84">
-        <f>[2]EB1!N17</f>
+        <f>'[2]EB1'!N17</f>
         <v>0</v>
       </c>
       <c r="O6" s="83">
-        <f>[2]EB1!O17</f>
+        <f>'[2]EB1'!O17</f>
         <v>39</v>
       </c>
       <c r="P6" s="83">
-        <f>[2]EB1!P17</f>
+        <f>'[2]EB1'!P17</f>
         <v>0</v>
       </c>
       <c r="Q6" s="83">
-        <f>[2]EB1!Q17</f>
+        <f>'[2]EB1'!Q17</f>
         <v>0</v>
       </c>
       <c r="R6" s="83">
-        <f>[2]EB1!R17</f>
+        <f>'[2]EB1'!R17</f>
         <v>7.5</v>
       </c>
       <c r="S6" s="83">
-        <f>[2]EB1!S17</f>
+        <f>'[2]EB1'!S17</f>
         <v>0.60850000000000004</v>
       </c>
       <c r="T6" s="83">
-        <f>[2]EB1!T17</f>
+        <f>'[2]EB1'!T17</f>
         <v>127.32299999999999</v>
       </c>
       <c r="U6" s="83">
-        <f>[2]EB1!U17</f>
+        <f>'[2]EB1'!U17</f>
         <v>1263.6955</v>
       </c>
       <c r="V6" s="85">
-        <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
+        <f t="shared" si="0" ref="V6:V12">SUM(D6:U6)</f>
         <v>2603.2252500000004</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:22" ht="12.75">
       <c r="B7" s="43" t="s">
         <v>62</v>
       </c>
@@ -5207,75 +5168,75 @@
         <v>63</v>
       </c>
       <c r="D7" s="83">
-        <f>[2]EB1!D18</f>
+        <f>'[2]EB1'!D18</f>
         <v>1233.0409000000002</v>
       </c>
       <c r="E7" s="83">
-        <f>[2]EB1!E18</f>
+        <f>'[2]EB1'!E18</f>
         <v>1774.8644000000002</v>
       </c>
       <c r="F7" s="83">
-        <f>[2]EB1!F18</f>
+        <f>'[2]EB1'!F18</f>
         <v>0</v>
       </c>
       <c r="G7" s="83">
-        <f>[2]EB1!G18</f>
-        <v>298.68</v>
+        <f>'[2]EB1'!G18</f>
+        <v>298.68000000000001</v>
       </c>
       <c r="H7" s="83">
-        <f>[2]EB1!H18</f>
+        <f>'[2]EB1'!H18</f>
         <v>36.356499999999997</v>
       </c>
       <c r="I7" s="83">
-        <f>[2]EB1!I18</f>
+        <f>'[2]EB1'!I18</f>
         <v>142.97149999999999</v>
       </c>
       <c r="J7" s="83">
-        <f>[2]EB1!J18</f>
+        <f>'[2]EB1'!J18</f>
         <v>7.766</v>
       </c>
       <c r="K7" s="83">
-        <f>[2]EB1!K18</f>
+        <f>'[2]EB1'!K18</f>
         <v>44.066000000000003</v>
       </c>
       <c r="L7" s="83">
-        <f>[2]EB1!L18</f>
+        <f>'[2]EB1'!L18</f>
         <v>286.0505</v>
       </c>
       <c r="M7" s="83">
-        <f>[2]EB1!M18</f>
+        <f>'[2]EB1'!M18</f>
         <v>191.57300000000001</v>
       </c>
       <c r="N7" s="84">
-        <f>[2]EB1!N18</f>
+        <f>'[2]EB1'!N18</f>
         <v>0</v>
       </c>
       <c r="O7" s="83">
-        <f>[2]EB1!O18</f>
+        <f>'[2]EB1'!O18</f>
         <v>541.25324999999998</v>
       </c>
       <c r="P7" s="83">
-        <f>[2]EB1!P18</f>
+        <f>'[2]EB1'!P18</f>
         <v>0</v>
       </c>
       <c r="Q7" s="83">
-        <f>[2]EB1!Q18</f>
+        <f>'[2]EB1'!Q18</f>
         <v>0</v>
       </c>
       <c r="R7" s="83">
-        <f>[2]EB1!R18</f>
+        <f>'[2]EB1'!R18</f>
         <v>0</v>
       </c>
       <c r="S7" s="83">
-        <f>[2]EB1!S18</f>
+        <f>'[2]EB1'!S18</f>
         <v>58.595999999999997</v>
       </c>
       <c r="T7" s="83">
-        <f>[2]EB1!T18</f>
+        <f>'[2]EB1'!T18</f>
         <v>316.79149999999998</v>
       </c>
       <c r="U7" s="83">
-        <f>[2]EB1!U18</f>
+        <f>'[2]EB1'!U18</f>
         <v>2044.222</v>
       </c>
       <c r="V7" s="85">
@@ -5283,7 +5244,7 @@
         <v>6976.2315499999995</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" ht="12.75">
       <c r="B8" s="43" t="s">
         <v>64</v>
       </c>
@@ -5291,75 +5252,75 @@
         <v>65</v>
       </c>
       <c r="D8" s="83">
-        <f>[2]EB1!D19</f>
+        <f>'[2]EB1'!D19</f>
         <v>28.665000000000003</v>
       </c>
       <c r="E8" s="83">
-        <f>[2]EB1!E19</f>
+        <f>'[2]EB1'!E19</f>
         <v>80.482399999999998</v>
       </c>
       <c r="F8" s="83">
-        <f>[2]EB1!F19</f>
+        <f>'[2]EB1'!F19</f>
         <v>0</v>
       </c>
       <c r="G8" s="83">
-        <f>[2]EB1!G19</f>
+        <f>'[2]EB1'!G19</f>
         <v>366.58800000000002</v>
       </c>
       <c r="H8" s="83">
-        <f>[2]EB1!H19</f>
+        <f>'[2]EB1'!H19</f>
         <v>0.47299999999999998</v>
       </c>
       <c r="I8" s="83">
-        <f>[2]EB1!I19</f>
+        <f>'[2]EB1'!I19</f>
         <v>16.169</v>
       </c>
       <c r="J8" s="83">
-        <f>[2]EB1!J19</f>
+        <f>'[2]EB1'!J19</f>
         <v>1.716</v>
       </c>
       <c r="K8" s="83">
-        <f>[2]EB1!K19</f>
+        <f>'[2]EB1'!K19</f>
         <v>0</v>
       </c>
       <c r="L8" s="83">
-        <f>[2]EB1!L19</f>
+        <f>'[2]EB1'!L19</f>
         <v>13.74</v>
       </c>
       <c r="M8" s="83">
-        <f>[2]EB1!M19</f>
+        <f>'[2]EB1'!M19</f>
         <v>0</v>
       </c>
       <c r="N8" s="84">
-        <f>[2]EB1!N19</f>
+        <f>'[2]EB1'!N19</f>
         <v>0</v>
       </c>
       <c r="O8" s="83">
-        <f>[2]EB1!O19</f>
+        <f>'[2]EB1'!O19</f>
         <v>47.314499999999995</v>
       </c>
       <c r="P8" s="83">
-        <f>[2]EB1!P19</f>
+        <f>'[2]EB1'!P19</f>
         <v>0</v>
       </c>
       <c r="Q8" s="83">
-        <f>[2]EB1!Q19</f>
+        <f>'[2]EB1'!Q19</f>
         <v>0</v>
       </c>
       <c r="R8" s="83">
-        <f>[2]EB1!R19</f>
+        <f>'[2]EB1'!R19</f>
         <v>0</v>
       </c>
       <c r="S8" s="83">
-        <f>[2]EB1!S19</f>
-        <v>5.0000000000000001E-4</v>
+        <f>'[2]EB1'!S19</f>
+        <v>0.00050000000000000001</v>
       </c>
       <c r="T8" s="83">
-        <f>[2]EB1!T19</f>
+        <f>'[2]EB1'!T19</f>
         <v>7.7869999999999999</v>
       </c>
       <c r="U8" s="83">
-        <f>[2]EB1!U19</f>
+        <f>'[2]EB1'!U19</f>
         <v>9.6930000000000014</v>
       </c>
       <c r="V8" s="85">
@@ -5367,7 +5328,7 @@
         <v>572.62840000000006</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" ht="15">
       <c r="B9" s="43" t="s">
         <v>66</v>
       </c>
@@ -5375,75 +5336,75 @@
         <v>67</v>
       </c>
       <c r="D9" s="83">
-        <f>[2]EB1!D20</f>
+        <f>'[2]EB1'!D20</f>
         <v>0.36140000000000005</v>
       </c>
       <c r="E9" s="47">
-        <f>[2]EB1!E20</f>
+        <f>'[2]EB1'!E20</f>
         <v>8.4995999999999992</v>
       </c>
       <c r="F9" s="83">
-        <f>[2]EB1!F20</f>
+        <f>'[2]EB1'!F20</f>
         <v>0</v>
       </c>
       <c r="G9" s="47">
-        <f>[2]EB1!G20</f>
+        <f>'[2]EB1'!G20</f>
         <v>3856.2855</v>
       </c>
       <c r="H9" s="83">
-        <f>[2]EB1!H20</f>
+        <f>'[2]EB1'!H20</f>
         <v>1047.652</v>
       </c>
       <c r="I9" s="47">
-        <f>[2]EB1!I20</f>
+        <f>'[2]EB1'!I20</f>
         <v>94.230999999999995</v>
       </c>
       <c r="J9" s="47">
-        <f>[2]EB1!J20</f>
+        <f>'[2]EB1'!J20</f>
         <v>2394.2159999999999</v>
       </c>
       <c r="K9" s="83">
-        <f>[2]EB1!K20</f>
+        <f>'[2]EB1'!K20</f>
         <v>0</v>
       </c>
       <c r="L9" s="83">
-        <f>[2]EB1!L20</f>
-        <v>33.24</v>
+        <f>'[2]EB1'!L20</f>
+        <v>33.240000000000002</v>
       </c>
       <c r="M9" s="83">
-        <f>[2]EB1!M20</f>
+        <f>'[2]EB1'!M20</f>
         <v>0</v>
       </c>
       <c r="N9" s="83">
-        <f>[2]EB1!N20</f>
+        <f>'[2]EB1'!N20</f>
         <v>0</v>
       </c>
       <c r="O9" s="47">
-        <f>[2]EB1!O20</f>
+        <f>'[2]EB1'!O20</f>
         <v>120.75</v>
       </c>
       <c r="P9" s="83">
-        <f>[2]EB1!P20</f>
+        <f>'[2]EB1'!P20</f>
         <v>0</v>
       </c>
       <c r="Q9" s="83">
-        <f>[2]EB1!Q20</f>
+        <f>'[2]EB1'!Q20</f>
         <v>0</v>
       </c>
       <c r="R9" s="83">
-        <f>[2]EB1!R20</f>
+        <f>'[2]EB1'!R20</f>
         <v>0</v>
       </c>
       <c r="S9" s="83">
-        <f>[2]EB1!S20</f>
+        <f>'[2]EB1'!S20</f>
         <v>0</v>
       </c>
       <c r="T9" s="83">
-        <f>[2]EB1!T20</f>
+        <f>'[2]EB1'!T20</f>
         <v>0</v>
       </c>
       <c r="U9" s="47">
-        <f>[2]EB1!U20</f>
+        <f>'[2]EB1'!U20</f>
         <v>132.98599999999999</v>
       </c>
       <c r="V9" s="85">
@@ -5451,7 +5412,7 @@
         <v>7688.2214999999987</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:22" ht="12.75">
       <c r="B10" s="43" t="s">
         <v>68</v>
       </c>
@@ -5459,75 +5420,75 @@
         <v>69</v>
       </c>
       <c r="D10" s="46">
-        <f>[2]EB1!D21</f>
+        <f>'[2]EB1'!D21</f>
         <v>773.00014999999871</v>
       </c>
       <c r="E10" s="46">
-        <f>[2]EB1!E21</f>
+        <f>'[2]EB1'!E21</f>
         <v>0</v>
       </c>
       <c r="F10" s="46">
-        <f>[2]EB1!F21</f>
+        <f>'[2]EB1'!F21</f>
         <v>0</v>
       </c>
       <c r="G10" s="46">
-        <f>[2]EB1!G21</f>
+        <f>'[2]EB1'!G21</f>
         <v>0</v>
       </c>
       <c r="H10" s="46">
-        <f>[2]EB1!H21</f>
+        <f>'[2]EB1'!H21</f>
         <v>0</v>
       </c>
       <c r="I10" s="46">
-        <f>[2]EB1!I21</f>
+        <f>'[2]EB1'!I21</f>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f>[2]EB1!J21</f>
+        <f>'[2]EB1'!J21</f>
         <v>0</v>
       </c>
       <c r="K10" s="46">
-        <f>[2]EB1!K21</f>
+        <f>'[2]EB1'!K21</f>
         <v>0</v>
       </c>
       <c r="L10" s="46">
-        <f>[2]EB1!L21</f>
+        <f>'[2]EB1'!L21</f>
         <v>0</v>
       </c>
       <c r="M10" s="46">
-        <f>[2]EB1!M21</f>
+        <f>'[2]EB1'!M21</f>
         <v>0</v>
       </c>
       <c r="N10" s="46">
-        <f>[2]EB1!N21</f>
+        <f>'[2]EB1'!N21</f>
         <v>0</v>
       </c>
       <c r="O10" s="46">
-        <f>[2]EB1!O21</f>
+        <f>'[2]EB1'!O21</f>
         <v>0</v>
       </c>
       <c r="P10" s="46">
-        <f>[2]EB1!P21</f>
+        <f>'[2]EB1'!P21</f>
         <v>0</v>
       </c>
       <c r="Q10" s="46">
-        <f>[2]EB1!Q21</f>
+        <f>'[2]EB1'!Q21</f>
         <v>0</v>
       </c>
       <c r="R10" s="46">
-        <f>[2]EB1!R21</f>
+        <f>'[2]EB1'!R21</f>
         <v>0</v>
       </c>
       <c r="S10" s="46">
-        <f>[2]EB1!S21</f>
+        <f>'[2]EB1'!S21</f>
         <v>0</v>
       </c>
       <c r="T10" s="46">
-        <f>[2]EB1!T21</f>
+        <f>'[2]EB1'!T21</f>
         <v>313.51900000000001</v>
       </c>
       <c r="U10" s="46">
-        <f>[2]EB1!U21</f>
+        <f>'[2]EB1'!U21</f>
         <v>325</v>
       </c>
       <c r="V10" s="86">
@@ -5535,7 +5496,7 @@
         <v>1411.5191499999987</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" ht="12.75">
       <c r="B11" s="43" t="s">
         <v>86</v>
       </c>
@@ -5543,75 +5504,75 @@
         <v>70</v>
       </c>
       <c r="D11" s="83">
-        <f>[2]EB1!D22</f>
+        <f>'[2]EB1'!D22</f>
         <v>34.094450000000002</v>
       </c>
       <c r="E11" s="83">
-        <f>[2]EB1!E22</f>
+        <f>'[2]EB1'!E22</f>
         <v>253.5292</v>
       </c>
       <c r="F11" s="83">
-        <f>[2]EB1!F22</f>
+        <f>'[2]EB1'!F22</f>
         <v>0</v>
       </c>
       <c r="G11" s="83">
-        <f>[2]EB1!G22</f>
+        <f>'[2]EB1'!G22</f>
         <v>76.465000000000003</v>
       </c>
       <c r="H11" s="83">
-        <f>[2]EB1!H22</f>
+        <f>'[2]EB1'!H22</f>
         <v>4.7945000000000002</v>
       </c>
       <c r="I11" s="83">
-        <f>[2]EB1!I22</f>
+        <f>'[2]EB1'!I22</f>
         <v>199.87350000000001</v>
       </c>
       <c r="J11" s="83">
-        <f>[2]EB1!J22</f>
+        <f>'[2]EB1'!J22</f>
         <v>3.1459999999999999</v>
       </c>
       <c r="K11" s="83">
-        <f>[2]EB1!K22</f>
+        <f>'[2]EB1'!K22</f>
         <v>899.20600000000002</v>
       </c>
       <c r="L11" s="83">
-        <f>[2]EB1!L22</f>
-        <v>52.04</v>
+        <f>'[2]EB1'!L22</f>
+        <v>52.039999999999999</v>
       </c>
       <c r="M11" s="83">
-        <f>[2]EB1!M22</f>
+        <f>'[2]EB1'!M22</f>
         <v>800.72900000000004</v>
       </c>
       <c r="N11" s="84">
-        <f>[2]EB1!N22</f>
+        <f>'[2]EB1'!N22</f>
         <v>0</v>
       </c>
       <c r="O11" s="83">
-        <f>[2]EB1!O22</f>
+        <f>'[2]EB1'!O22</f>
         <v>0</v>
       </c>
       <c r="P11" s="83">
-        <f>[2]EB1!P22</f>
+        <f>'[2]EB1'!P22</f>
         <v>0</v>
       </c>
       <c r="Q11" s="83">
-        <f>[2]EB1!Q22</f>
+        <f>'[2]EB1'!Q22</f>
         <v>0</v>
       </c>
       <c r="R11" s="83">
-        <f>[2]EB1!R22</f>
+        <f>'[2]EB1'!R22</f>
         <v>0</v>
       </c>
       <c r="S11" s="83">
-        <f>[2]EB1!S22</f>
+        <f>'[2]EB1'!S22</f>
         <v>0</v>
       </c>
       <c r="T11" s="83">
-        <f>[2]EB1!T22</f>
+        <f>'[2]EB1'!T22</f>
         <v>0</v>
       </c>
       <c r="U11" s="83">
-        <f>[2]EB1!U22</f>
+        <f>'[2]EB1'!U22</f>
         <v>0</v>
       </c>
       <c r="V11" s="85">
@@ -5619,7 +5580,7 @@
         <v>2323.8776500000004</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:22" ht="12.75">
       <c r="B12" s="43" t="s">
         <v>87</v>
       </c>
@@ -5627,75 +5588,75 @@
         <v>71</v>
       </c>
       <c r="D12" s="83">
-        <f>[2]EB1!D23</f>
+        <f>'[2]EB1'!D23</f>
         <v>0</v>
       </c>
       <c r="E12" s="83">
-        <f>[2]EB1!E23</f>
+        <f>'[2]EB1'!E23</f>
         <v>0</v>
       </c>
       <c r="F12" s="83">
-        <f>[2]EB1!F23</f>
+        <f>'[2]EB1'!F23</f>
         <v>0</v>
       </c>
       <c r="G12" s="83">
-        <f>[2]EB1!G23</f>
+        <f>'[2]EB1'!G23</f>
         <v>146.90600000000001</v>
       </c>
       <c r="H12" s="83">
-        <f>[2]EB1!H23</f>
+        <f>'[2]EB1'!H23</f>
         <v>0</v>
       </c>
       <c r="I12" s="83">
-        <f>[2]EB1!I23</f>
+        <f>'[2]EB1'!I23</f>
         <v>0</v>
       </c>
       <c r="J12" s="83">
-        <f>[2]EB1!J23</f>
+        <f>'[2]EB1'!J23</f>
         <v>0</v>
       </c>
       <c r="K12" s="83">
-        <f>[2]EB1!K23</f>
+        <f>'[2]EB1'!K23</f>
         <v>0</v>
       </c>
       <c r="L12" s="83">
-        <f>[2]EB1!L23</f>
-        <v>902.14</v>
+        <f>'[2]EB1'!L23</f>
+        <v>902.13999999999999</v>
       </c>
       <c r="M12" s="83">
-        <f>[2]EB1!M23</f>
+        <f>'[2]EB1'!M23</f>
         <v>6.5</v>
       </c>
       <c r="N12" s="84">
-        <f>[2]EB1!N23</f>
+        <f>'[2]EB1'!N23</f>
         <v>0</v>
       </c>
       <c r="O12" s="46">
-        <f>[2]EB1!O23</f>
+        <f>'[2]EB1'!O23</f>
         <v>0</v>
       </c>
       <c r="P12" s="46">
-        <f>[2]EB1!P23</f>
+        <f>'[2]EB1'!P23</f>
         <v>0</v>
       </c>
       <c r="Q12" s="46">
-        <f>[2]EB1!Q23</f>
+        <f>'[2]EB1'!Q23</f>
         <v>0</v>
       </c>
       <c r="R12" s="46">
-        <f>[2]EB1!R23</f>
+        <f>'[2]EB1'!R23</f>
         <v>0</v>
       </c>
       <c r="S12" s="83">
-        <f>[2]EB1!S23</f>
+        <f>'[2]EB1'!S23</f>
         <v>0</v>
       </c>
       <c r="T12" s="83">
-        <f>[2]EB1!T23</f>
+        <f>'[2]EB1'!T23</f>
         <v>0</v>
       </c>
       <c r="U12" s="83">
-        <f>[2]EB1!U23</f>
+        <f>'[2]EB1'!U23</f>
         <v>0</v>
       </c>
       <c r="V12" s="85">
@@ -5703,7 +5664,7 @@
         <v>1055.546</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" ht="15">
       <c r="B13" s="80" t="s">
         <v>89</v>
       </c>
@@ -5711,7 +5672,7 @@
         <v>162</v>
       </c>
       <c r="D13" s="48">
-        <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
+        <f t="shared" si="1" ref="D13:V13">SUM(D5:D12)</f>
         <v>2337.9238999999989</v>
       </c>
       <c r="E13" s="48">
@@ -5778,7 +5739,7 @@
         <v>28885.632699999998</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:13" ht="12.75">
       <c r="D14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -5789,7 +5750,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="4:13" ht="12.75">
       <c r="D15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -5800,7 +5761,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="15">
       <c r="C16" s="47" t="s">
         <v>157</v>
       </c>
@@ -5815,7 +5776,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:13" ht="12.75">
       <c r="D17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -5826,7 +5787,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:13" ht="12.75">
       <c r="D18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -5837,7 +5798,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:13" ht="12.75">
       <c r="D19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -5848,7 +5809,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:13" ht="12.75">
       <c r="D20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -5859,7 +5820,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:13" ht="12.75">
       <c r="D21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -5870,7 +5831,7 @@
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:13" ht="12.75">
       <c r="D22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -5881,11 +5842,11 @@
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:4" ht="12.75">
       <c r="C23" s="1"/>
       <c r="D23" s="21"/>
     </row>
-    <row r="24" spans="2:24" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:22" ht="38.25">
       <c r="B24" s="22" t="s">
         <v>102</v>
       </c>
@@ -5950,7 +5911,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" ht="15">
       <c r="B25" s="43" t="s">
         <v>66</v>
       </c>
@@ -5963,7 +5924,7 @@
       </c>
       <c r="F25" s="91"/>
       <c r="G25" s="94">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="H25" s="91"/>
       <c r="I25" s="94">
@@ -5992,7 +5953,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" ht="15">
       <c r="B26" s="43" t="s">
         <v>66</v>
       </c>
@@ -6007,7 +5968,7 @@
       <c r="F26" s="93"/>
       <c r="G26" s="96">
         <f>1-G25</f>
-        <v>9.9999999999999978E-2</v>
+        <v>0.099999999999999978</v>
       </c>
       <c r="H26" s="93"/>
       <c r="I26" s="96">
@@ -6040,7 +6001,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:5" ht="12.75">
       <c r="C29" s="58" t="s">
         <v>106</v>
       </c>
@@ -6051,7 +6012,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:5" ht="12.75">
       <c r="B30" s="20" t="s">
         <v>117</v>
       </c>
@@ -6065,7 +6026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:5" ht="12.75">
       <c r="B31" s="43" t="s">
         <v>66</v>
       </c>
@@ -6077,27 +6038,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:G5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="1.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="7.71428571428571" customWidth="1"/>
+    <col min="3" max="3" width="6.85714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" ht="18">
       <c r="B3" s="71" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="4:7" ht="12.75">
       <c r="D5" s="72" t="s">
         <v>166</v>
       </c>
@@ -6107,37 +6068,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R36"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28571428571429" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="7.14285714285714" customWidth="1"/>
+    <col min="12" max="12" width="14.5714285714286" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
+    <col min="15" max="15" width="10.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -6158,7 +6119,7 @@
       </c>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.75">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
@@ -6194,7 +6155,7 @@
       <c r="Q2" s="117"/>
       <c r="R2" s="117"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="10:18" ht="12.75">
       <c r="J3" s="118" t="s">
         <v>7</v>
       </c>
@@ -6223,7 +6184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="24" thickBot="1">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -6257,7 +6218,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:18" ht="12.75">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="70"/>
@@ -6275,7 +6236,7 @@
         <v>Transport Natural Gas</v>
       </c>
       <c r="N5" s="121" t="str">
-        <f t="shared" ref="N5:N10" si="0">$E$2</f>
+        <f t="shared" si="0" ref="N5:N10">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O5" s="121"/>
@@ -6283,7 +6244,7 @@
       <c r="Q5" s="121"/>
       <c r="R5" s="121"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="5:18" ht="12.75">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="70"/>
@@ -6307,7 +6268,7 @@
       <c r="Q6" s="121"/>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="5:18" ht="12.75">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="70"/>
@@ -6331,7 +6292,7 @@
       <c r="Q7" s="121"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:18" ht="12.75">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="70"/>
@@ -6355,7 +6316,7 @@
       <c r="Q8" s="121"/>
       <c r="R8" s="121"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:18" ht="12.75">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="70"/>
@@ -6379,7 +6340,7 @@
       <c r="Q9" s="121"/>
       <c r="R9" s="121"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="5:18" ht="12.75">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="70"/>
@@ -6407,11 +6368,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="12:13" ht="12.75">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="4:18" ht="12.75">
       <c r="D12" s="5" t="s">
         <v>13</v>
       </c>
@@ -6429,7 +6390,7 @@
       <c r="Q12" s="121"/>
       <c r="R12" s="121"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" ht="12.75">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -6479,7 +6440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" ht="23.25" thickBot="1">
       <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
@@ -6529,7 +6490,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1">
       <c r="B15" s="15" t="s">
         <v>91</v>
       </c>
@@ -6556,17 +6517,17 @@
       <c r="Q15" s="123"/>
       <c r="R15" s="123"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" ht="12.75">
       <c r="B16" t="str">
-        <f t="shared" ref="B16:B21" si="1">L16</f>
+        <f t="shared" si="1" ref="B16:B21">L16</f>
         <v>FTE-TRAGAS</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" ref="C16:C21" si="2">RIGHT(D16,3)</f>
+        <f t="shared" si="2" ref="C16:C21">RIGHT(D16,3)</f>
         <v>GAS</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" ref="D16:D21" si="3">L5</f>
+        <f t="shared" si="3" ref="D16:D21">L5</f>
         <v>TRAGAS</v>
       </c>
       <c r="E16" s="12"/>
@@ -6582,26 +6543,26 @@
       </c>
       <c r="K16" s="121"/>
       <c r="L16" s="121" t="str">
-        <f t="shared" ref="L16:L21" si="4">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <f t="shared" si="4" ref="L16:L21">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-TRAGAS</v>
       </c>
       <c r="M16" s="122" t="str">
-        <f t="shared" ref="M16:M21" si="5">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <f t="shared" si="5" ref="M16:M21">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Transport Natural Gas</v>
       </c>
       <c r="N16" s="121" t="str">
-        <f t="shared" ref="N16:N21" si="6">$E$2</f>
+        <f t="shared" si="6" ref="N16:N21">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O16" s="121" t="str">
-        <f t="shared" ref="O16:O21" si="7">$E$2&amp;"a"</f>
+        <f t="shared" si="7" ref="O16:O21">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P16" s="121"/>
       <c r="Q16" s="121"/>
       <c r="R16" s="121"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" ht="12.75">
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRADSL</v>
@@ -6644,7 +6605,7 @@
       <c r="Q17" s="121"/>
       <c r="R17" s="121"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" ht="12.75">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRALPG</v>
@@ -6687,7 +6648,7 @@
       <c r="Q18" s="121"/>
       <c r="R18" s="121"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" ht="12.75">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRAGSL</v>
@@ -6730,7 +6691,7 @@
       <c r="Q19" s="121"/>
       <c r="R19" s="121"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" ht="12.75">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRABIO</v>
@@ -6773,7 +6734,7 @@
       <c r="Q20" s="121"/>
       <c r="R20" s="121"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" ht="12.75">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRAELC</v>
@@ -6818,21 +6779,21 @@
       <c r="Q21" s="121"/>
       <c r="R21" s="121"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:13" ht="12.75">
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="70"/>
       <c r="H22" s="11"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:13" ht="12.75">
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="70"/>
       <c r="H23" s="11"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" ht="12.75">
       <c r="B24" s="23"/>
       <c r="D24" s="23"/>
       <c r="E24" s="12"/>
@@ -6841,7 +6802,7 @@
       <c r="H24" s="11"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" ht="12.75">
       <c r="B25" s="23"/>
       <c r="D25" s="23"/>
       <c r="E25" s="12"/>
@@ -6852,7 +6813,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" ht="12.75">
       <c r="B26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="98"/>
@@ -6863,7 +6824,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="12.75">
       <c r="B27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="98"/>
@@ -6874,7 +6835,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" ht="12.75">
       <c r="B28" s="23"/>
       <c r="D28" s="23"/>
       <c r="E28" s="98"/>
@@ -6883,7 +6844,7 @@
       <c r="H28" s="11"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" ht="12.75">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="98"/>
@@ -6891,7 +6852,7 @@
       <c r="G29" s="70"/>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" ht="12.75">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="12"/>
@@ -6899,7 +6860,7 @@
       <c r="G30" s="70"/>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" ht="12.75">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="12"/>
@@ -6907,13 +6868,13 @@
       <c r="G31" s="70"/>
       <c r="H31" s="11"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3" ht="12.75">
       <c r="B35" s="45"/>
       <c r="C35" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3" ht="12.75">
       <c r="B36" s="64"/>
       <c r="C36" s="1" t="s">
         <v>160</v>
@@ -6921,43 +6882,43 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:W32"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1428571428571" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="12.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85714285714286" customWidth="1"/>
+    <col min="11" max="11" width="13.5714285714286" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.8571428571429" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.4285714285714" customWidth="1"/>
+    <col min="16" max="16" width="7.14285714285714" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="63.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.7109375" customWidth="1"/>
+    <col min="18" max="18" width="63.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.71428571428571" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.2857142857143" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -6981,7 +6942,7 @@
       </c>
       <c r="I1" s="30"/>
     </row>
-    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" ht="31.5">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
@@ -7020,7 +6981,7 @@
       <c r="V2" s="117"/>
       <c r="W2" s="117"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="15:23" ht="12.75">
       <c r="O3" s="118" t="s">
         <v>7</v>
       </c>
@@ -7049,7 +7010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" ht="24" thickBot="1">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7083,7 +7044,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" ht="15.75">
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7098,7 +7059,7 @@
         <v>DTCAR</v>
       </c>
       <c r="R5" s="117" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$25</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp;" Sector - "&amp;'EB1'!$X$25</f>
         <v>Demand Transport Sector - Cars</v>
       </c>
       <c r="S5" s="117" t="s">
@@ -7109,7 +7070,7 @@
       <c r="V5" s="117"/>
       <c r="W5" s="117"/>
     </row>
-    <row r="6" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" ht="15.75">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -7122,7 +7083,7 @@
         <v>DTPUB</v>
       </c>
       <c r="R6" s="117" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$26</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp;" Sector - "&amp;'EB1'!$X$26</f>
         <v>Demand Transport Sector - Pub</v>
       </c>
       <c r="S6" s="117" t="s">
@@ -7133,7 +7094,7 @@
       <c r="V6" s="117"/>
       <c r="W6" s="117"/>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="15:23" ht="12.75">
       <c r="O7" s="121" t="s">
         <v>105</v>
       </c>
@@ -7155,7 +7116,7 @@
       <c r="V7" s="121"/>
       <c r="W7" s="121"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="4:23" ht="12.75">
       <c r="D9" s="5" t="s">
         <v>13</v>
       </c>
@@ -7175,7 +7136,7 @@
       <c r="V9" s="121"/>
       <c r="W9" s="121"/>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:23" ht="12.75">
       <c r="B10" s="17" t="s">
         <v>1</v>
       </c>
@@ -7238,7 +7199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" ht="23.25" thickBot="1">
       <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
@@ -7301,7 +7262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" ht="13.5" thickBot="1">
       <c r="B12" s="15" t="s">
         <v>91</v>
       </c>
@@ -7346,17 +7307,17 @@
       <c r="V12" s="120"/>
       <c r="W12" s="120"/>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23" ht="12.75">
       <c r="B13" t="str">
-        <f t="shared" ref="B13:B24" si="0">Q13</f>
+        <f t="shared" si="0" ref="B13:B24">Q13</f>
         <v>TCAREGAS</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" ref="C13:C24" si="1">$B$2&amp;RIGHT(B13,3)</f>
+        <f t="shared" si="1" ref="C13:C24">$B$2&amp;RIGHT(B13,3)</f>
         <v>TRAGAS</v>
       </c>
       <c r="D13" t="str">
-        <f t="shared" ref="D13:D18" si="2">$Q$5</f>
+        <f t="shared" si="2" ref="D13:D18">$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E13" s="63">
@@ -7379,7 +7340,7 @@
         <v>10</v>
       </c>
       <c r="K13" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M13" s="29">
         <f>E13*G13*K13*H13</f>
@@ -7394,14 +7355,14 @@
         <v>TCAREGAS</v>
       </c>
       <c r="R13" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$E$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Natural Gas</v>
       </c>
       <c r="S13" s="126" t="s">
         <v>183</v>
       </c>
       <c r="T13" s="117" t="str">
-        <f t="shared" ref="T13:T24" si="3">$G$2</f>
+        <f t="shared" si="3" ref="T13:T24">$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U13" s="121"/>
@@ -7410,7 +7371,7 @@
       </c>
       <c r="W13" s="121"/>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23" ht="12.75">
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>TCAREDSL</v>
@@ -7431,7 +7392,7 @@
         <v>0.41</v>
       </c>
       <c r="G14" s="62">
-        <v>16.5</v>
+        <v>16.50</v>
       </c>
       <c r="H14" s="67">
         <v>1.25</v>
@@ -7443,10 +7404,10 @@
         <v>10</v>
       </c>
       <c r="K14" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M14" s="29">
-        <f t="shared" ref="M14:M22" si="4">E14*G14*K14*H14</f>
+        <f t="shared" si="4" ref="M14:M22">E14*G14*K14*H14</f>
         <v>1796.4988037437502</v>
       </c>
       <c r="O14" s="121"/>
@@ -7456,7 +7417,7 @@
         <v>TCAREDSL</v>
       </c>
       <c r="R14" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$G$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Diesel oil</v>
       </c>
       <c r="S14" s="117" t="s">
@@ -7472,7 +7433,7 @@
       </c>
       <c r="W14" s="121"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23" ht="12.75">
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>TCARELPG</v>
@@ -7505,7 +7466,7 @@
         <v>10</v>
       </c>
       <c r="K15" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M15" s="29">
         <f t="shared" si="4"/>
@@ -7518,7 +7479,7 @@
         <v>TCARELPG</v>
       </c>
       <c r="R15" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$I$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - LPG</v>
       </c>
       <c r="S15" s="117" t="s">
@@ -7534,7 +7495,7 @@
       </c>
       <c r="W15" s="121"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23" ht="12.75">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>TCAREGSL</v>
@@ -7552,10 +7513,10 @@
         <v>84109.849043478273</v>
       </c>
       <c r="F16" s="68">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G16" s="62">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H16" s="67">
         <v>1.25</v>
@@ -7567,7 +7528,7 @@
         <v>10</v>
       </c>
       <c r="K16" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M16" s="29">
         <f t="shared" si="4"/>
@@ -7580,7 +7541,7 @@
         <v>TCAREGSL</v>
       </c>
       <c r="R16" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$J$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Motor spirit</v>
       </c>
       <c r="S16" s="117" t="s">
@@ -7596,7 +7557,7 @@
       </c>
       <c r="W16" s="121"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:23" ht="12.75">
       <c r="B17" t="str">
         <f>Q17</f>
         <v>TCAREBIO</v>
@@ -7614,10 +7575,10 @@
         <v>3181.5</v>
       </c>
       <c r="F17" s="68">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G17" s="62">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H17" s="67">
         <v>1.25</v>
@@ -7629,7 +7590,7 @@
         <v>10</v>
       </c>
       <c r="K17" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M17" s="29">
         <f>E17*G17*K17*H17</f>
@@ -7642,7 +7603,7 @@
         <v>TCAREBIO</v>
       </c>
       <c r="R17" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!O3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!O3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Biofuels</v>
       </c>
       <c r="S17" s="117" t="s">
@@ -7658,7 +7619,7 @@
       </c>
       <c r="W17" s="121"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23" ht="12.75">
       <c r="B18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TCAREELC</v>
@@ -7676,10 +7637,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="99">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G18" s="100">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H18" s="101">
         <v>1.25</v>
@@ -7691,7 +7652,7 @@
         <v>10</v>
       </c>
       <c r="K18" s="103">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="104">
@@ -7705,7 +7666,7 @@
         <v>TCAREELC</v>
       </c>
       <c r="R18" s="124" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$U$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$25&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Electricity</v>
       </c>
       <c r="S18" s="125" t="s">
@@ -7721,7 +7682,7 @@
       </c>
       <c r="W18" s="124"/>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:23" ht="12.75">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGAS</v>
@@ -7731,7 +7692,7 @@
         <v>TRAGAS</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" ref="D19:D24" si="5">$Q$6</f>
+        <f t="shared" si="5" ref="D19:D24">$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E19" s="63">
@@ -7739,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="67">
-        <v>0.1</v>
+        <v>0.10</v>
       </c>
       <c r="G19" s="45">
         <v>50</v>
@@ -7754,7 +7715,7 @@
         <v>30</v>
       </c>
       <c r="K19" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M19" s="29">
         <f>E19*G19*K19*H19</f>
@@ -7767,7 +7728,7 @@
         <v>TPUBEGAS</v>
       </c>
       <c r="R19" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$E$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Natural Gas</v>
       </c>
       <c r="S19" s="117" t="s">
@@ -7783,7 +7744,7 @@
       </c>
       <c r="W19" s="121"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:23" ht="12.75">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEDSL</v>
@@ -7816,7 +7777,7 @@
         <v>30</v>
       </c>
       <c r="K20" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M20" s="29">
         <f>E20*G20*K20*H20</f>
@@ -7829,7 +7790,7 @@
         <v>TPUBEDSL</v>
       </c>
       <c r="R20" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$G$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Diesel oil</v>
       </c>
       <c r="S20" s="117" t="s">
@@ -7845,7 +7806,7 @@
       </c>
       <c r="W20" s="121"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23" ht="12.75">
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>TPUBELPG</v>
@@ -7863,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="67">
-        <v>0.1</v>
+        <v>0.10</v>
       </c>
       <c r="G21" s="62">
         <v>50</v>
@@ -7878,7 +7839,7 @@
         <v>30</v>
       </c>
       <c r="K21" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M21" s="29">
         <f>E21*G21*K21*H21</f>
@@ -7891,7 +7852,7 @@
         <v>TPUBELPG</v>
       </c>
       <c r="R21" s="122" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$I$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - LPG</v>
       </c>
       <c r="S21" s="117" t="s">
@@ -7907,7 +7868,7 @@
       </c>
       <c r="W21" s="121"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:23" ht="12.75">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGSL</v>
@@ -7940,7 +7901,7 @@
         <v>30</v>
       </c>
       <c r="K22" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M22" s="29">
         <f t="shared" si="4"/>
@@ -7953,7 +7914,7 @@
         <v>TPUBEGSL</v>
       </c>
       <c r="R22" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$J$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Motor spirit</v>
       </c>
       <c r="S22" s="117" t="s">
@@ -7969,7 +7930,7 @@
       </c>
       <c r="W22" s="121"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:23" ht="12.75">
       <c r="B23" t="str">
         <f>Q23</f>
         <v>TPUBEBIO</v>
@@ -8002,7 +7963,7 @@
         <v>30</v>
       </c>
       <c r="K23" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M23" s="29">
         <f>E23*G23*K23*H23</f>
@@ -8015,7 +7976,7 @@
         <v>TPUBEBIO</v>
       </c>
       <c r="R23" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!O3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!O3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Biofuels</v>
       </c>
       <c r="S23" s="117" t="s">
@@ -8031,7 +7992,7 @@
       </c>
       <c r="W23" s="121"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:23" ht="12.75">
       <c r="B24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEELC</v>
@@ -8064,7 +8025,7 @@
         <v>30</v>
       </c>
       <c r="K24" s="103">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M24" s="104">
         <f>E24*G24*K24*H24</f>
@@ -8077,7 +8038,7 @@
         <v>TPUBEELC</v>
       </c>
       <c r="R24" s="124" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$U$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB1'!$X$26&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Electricity</v>
       </c>
       <c r="S24" s="125" t="s">
@@ -8093,7 +8054,7 @@
       </c>
       <c r="W24" s="124"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="12.75">
       <c r="B27" s="45"/>
       <c r="C27" s="1" t="s">
         <v>159</v>
@@ -8102,7 +8063,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" ht="12.75">
       <c r="B28" s="64"/>
       <c r="C28" s="1" t="s">
         <v>160</v>
@@ -8112,49 +8073,49 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="11:14" ht="12.75">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="11:14" ht="12.75">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:14" ht="12.75">
       <c r="E31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:5" ht="12.75">
       <c r="E32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="11.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="11.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5714285714286" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -8171,7 +8132,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75">
       <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
@@ -8186,7 +8147,7 @@
         <v>M€2005</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:10" ht="12.75">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -8197,7 +8158,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" ht="12.75">
       <c r="B6" s="2" t="s">
         <v>80</v>
       </c>
@@ -8223,7 +8184,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" ht="22.5">
       <c r="B7" s="16" t="s">
         <v>81</v>
       </c>
@@ -8245,7 +8206,7 @@
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="13.5" thickBot="1">
       <c r="B8" s="15" t="s">
         <v>91</v>
       </c>
@@ -8262,7 +8223,7 @@
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" ht="12.75">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -8291,7 +8252,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:10" ht="12.75">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -8320,7 +8281,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="7:10" ht="12.75">
       <c r="G11" s="1" t="s">
         <v>120</v>
       </c>
@@ -8335,7 +8296,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="5:10" ht="12.75">
       <c r="E12" s="26"/>
       <c r="G12" s="27" t="s">
         <v>120</v>
@@ -8351,7 +8312,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:10" ht="12.75">
       <c r="E13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>120</v>
@@ -8367,7 +8328,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="7:10" ht="12.75">
       <c r="G14" s="1" t="s">
         <v>120</v>
       </c>
@@ -8382,7 +8343,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="5:10" ht="12.75">
       <c r="E15" s="7"/>
       <c r="G15" s="1" t="s">
         <v>120</v>
@@ -8398,7 +8359,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="7:10" ht="12.75">
       <c r="G16" s="1" t="s">
         <v>120</v>
       </c>
@@ -8413,13 +8374,13 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" ht="12.75">
       <c r="B23" s="45"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
@@ -8432,14 +8393,14 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:J28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="17.45" customHeight="1">
       <c r="B3" s="35" t="s">
         <v>149</v>
       </c>
@@ -8450,7 +8411,7 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
     </row>
-    <row r="4" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="17.45" customHeight="1">
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -8458,13 +8419,13 @@
       <c r="F4" s="36"/>
       <c r="G4" s="36"/>
     </row>
-    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="18">
       <c r="B5" s="33" t="s">
         <v>150</v>
       </c>
       <c r="C5" s="34"/>
     </row>
-    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13.5" thickBot="1">
       <c r="B6" s="38" t="s">
         <v>0</v>
       </c>
@@ -8488,7 +8449,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" thickBot="1">
       <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
@@ -8510,13 +8471,13 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9" ht="12.75">
       <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
       </c>
       <c r="C8" s="67">
-        <v>56.1</v>
+        <v>56.10</v>
       </c>
       <c r="D8" s="67">
         <v>75</v>
@@ -8531,32 +8492,32 @@
       <c r="H8" s="106"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="9:9" ht="12.75">
       <c r="I9" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="9:9" ht="12.75">
       <c r="I11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="9:9" ht="12.75">
       <c r="I12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="10:10" ht="12.75">
       <c r="J14" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="9:9" ht="12.75">
       <c r="I20" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" ht="12.75">
       <c r="B23" s="45"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
@@ -8565,13 +8526,13 @@
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="6:9" ht="12.75">
       <c r="F28" t="s">
         <v>191</v>
       </c>
